--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D7A10D-180F-6940-9091-BE39947CA342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D00CFB-5529-BF47-BD9D-90384999F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6340" yWindow="3000" windowWidth="27840" windowHeight="20620" activeTab="2" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="3880" yWindow="5600" windowWidth="33620" windowHeight="20620" activeTab="11" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="179">
   <si>
     <t>X</t>
   </si>
@@ -724,6 +724,9 @@
   </si>
   <si>
     <t>soil</t>
+  </si>
+  <si>
+    <t>pile</t>
   </si>
 </sst>
 </file>
@@ -1165,19 +1168,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1208,21 +1211,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
@@ -7815,6 +7804,12 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -7824,6 +7819,12 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-10</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -10782,11 +10783,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
@@ -11846,12 +11847,24 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="3">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3">
+        <v>-10</v>
+      </c>
+      <c r="G3" s="3">
+        <v>5000</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -13081,36 +13094,36 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="48" t="s">
+      <c r="L7" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48" t="s">
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="S7" s="48"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
-      <c r="V7" s="48"/>
-      <c r="W7" s="48" t="s">
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="47"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="X7" s="48"/>
+      <c r="X7" s="47"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
@@ -13898,38 +13911,33 @@
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="R7:V7"/>
   </mergeCells>
-  <conditionalFormatting sqref="F10:F50">
-    <cfRule type="expression" dxfId="10" priority="4">
-      <formula>$D10="cp"</formula>
+  <conditionalFormatting sqref="F9:F50">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:H50">
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:J50">
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9:N50">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:O50">
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="4" priority="14">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:Q50">
-    <cfRule type="expression" dxfId="5" priority="9">
-      <formula>$D9="cp"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="9">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13983,74 +13991,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="D4" s="51" t="s">
+      <c r="B4" s="49"/>
+      <c r="D4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="G4" s="51" t="s">
+      <c r="E4" s="49"/>
+      <c r="G4" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="51"/>
-      <c r="J4" s="51" t="s">
+      <c r="H4" s="49"/>
+      <c r="J4" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="51"/>
-      <c r="M4" s="51" t="s">
+      <c r="K4" s="49"/>
+      <c r="M4" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="51"/>
-      <c r="P4" s="51" t="s">
+      <c r="N4" s="49"/>
+      <c r="P4" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="51"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="51" t="s">
+      <c r="S4" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="51"/>
+      <c r="T4" s="49"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="51" t="s">
+      <c r="V4" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="51"/>
+      <c r="W4" s="49"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="51" t="s">
+      <c r="Y4" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="51"/>
+      <c r="Z4" s="49"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="51" t="s">
+      <c r="AB4" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="51"/>
-      <c r="AE4" s="51" t="s">
+      <c r="AC4" s="49"/>
+      <c r="AE4" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="AF4" s="51"/>
+      <c r="AF4" s="49"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="51" t="s">
+      <c r="AH4" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="AI4" s="51"/>
+      <c r="AI4" s="49"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="51" t="s">
+      <c r="AK4" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="AL4" s="51"/>
+      <c r="AL4" s="49"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="51" t="s">
+      <c r="AN4" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="AO4" s="51"/>
+      <c r="AO4" s="49"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="51" t="s">
+      <c r="AQ4" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="AR4" s="51"/>
+      <c r="AR4" s="49"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -14153,89 +14161,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="49" t="str">
+      <c r="A6" s="50" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="D6" s="49" t="str">
+      <c r="B6" s="51"/>
+      <c r="D6" s="50" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="50"/>
-      <c r="G6" s="49" t="str">
+      <c r="E6" s="51"/>
+      <c r="G6" s="50" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="50"/>
-      <c r="J6" s="49" t="str">
+      <c r="H6" s="51"/>
+      <c r="J6" s="50" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="50"/>
-      <c r="M6" s="49" t="str">
+      <c r="K6" s="51"/>
+      <c r="M6" s="50" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="50"/>
-      <c r="P6" s="49" t="str">
+      <c r="N6" s="51"/>
+      <c r="P6" s="50" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="50"/>
+      <c r="Q6" s="51"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="49" t="str">
+      <c r="S6" s="50" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="50"/>
+      <c r="T6" s="51"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="49" t="str">
+      <c r="V6" s="50" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="50"/>
+      <c r="W6" s="51"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="49" t="str">
+      <c r="Y6" s="50" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="50"/>
+      <c r="Z6" s="51"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="49" t="str">
+      <c r="AB6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="50"/>
-      <c r="AE6" s="49" t="str">
+      <c r="AC6" s="51"/>
+      <c r="AE6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="50"/>
+      <c r="AF6" s="51"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="49" t="str">
+      <c r="AH6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="50"/>
+      <c r="AI6" s="51"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="49" t="str">
+      <c r="AK6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="50"/>
+      <c r="AL6" s="51"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="49" t="str">
+      <c r="AN6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="50"/>
+      <c r="AO6" s="51"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="49" t="str">
+      <c r="AQ6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="50"/>
+      <c r="AR6" s="51"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -15155,36 +15163,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15222,74 +15230,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="D4" s="51" t="s">
+      <c r="B4" s="49"/>
+      <c r="D4" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="G4" s="51" t="s">
+      <c r="E4" s="49"/>
+      <c r="G4" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="51"/>
-      <c r="J4" s="51" t="s">
+      <c r="H4" s="49"/>
+      <c r="J4" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="K4" s="51"/>
-      <c r="M4" s="51" t="s">
+      <c r="K4" s="49"/>
+      <c r="M4" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="51"/>
-      <c r="P4" s="51" t="s">
+      <c r="N4" s="49"/>
+      <c r="P4" s="49" t="s">
         <v>158</v>
       </c>
-      <c r="Q4" s="51"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="51" t="s">
+      <c r="S4" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="T4" s="51"/>
+      <c r="T4" s="49"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="51" t="s">
+      <c r="V4" s="49" t="s">
         <v>160</v>
       </c>
-      <c r="W4" s="51"/>
+      <c r="W4" s="49"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="51" t="s">
+      <c r="Y4" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="Z4" s="51"/>
+      <c r="Z4" s="49"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="51" t="s">
+      <c r="AB4" s="49" t="s">
         <v>162</v>
       </c>
-      <c r="AC4" s="51"/>
-      <c r="AE4" s="51" t="s">
+      <c r="AC4" s="49"/>
+      <c r="AE4" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="AF4" s="51"/>
+      <c r="AF4" s="49"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="51" t="s">
+      <c r="AH4" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="AI4" s="51"/>
+      <c r="AI4" s="49"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="51" t="s">
+      <c r="AK4" s="49" t="s">
         <v>165</v>
       </c>
-      <c r="AL4" s="51"/>
+      <c r="AL4" s="49"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="51" t="s">
+      <c r="AN4" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="AO4" s="51"/>
+      <c r="AO4" s="49"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="51" t="s">
+      <c r="AQ4" s="49" t="s">
         <v>167</v>
       </c>
-      <c r="AR4" s="51"/>
+      <c r="AR4" s="49"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
@@ -16378,12 +16386,14 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AQ4:AR4"/>
@@ -16400,14 +16410,12 @@
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16773,24 +16781,19 @@
       <c r="N16" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E4:E42">
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>OR($D4="Intercept", $D4="Radius")</formula>
+  <conditionalFormatting sqref="E3:E42">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G42">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>OR($D3="Depth",$D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H42">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>OR($D3="Depth",$D3="Intercept")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D00CFB-5529-BF47-BD9D-90384999F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B0BEC2-B169-4F40-A0DC-06CF86F0024A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3880" yWindow="5600" windowWidth="33620" windowHeight="20620" activeTab="11" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="24840" yWindow="5860" windowWidth="37700" windowHeight="20620" activeTab="11" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -10123,7 +10123,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>426357</xdr:colOff>
+      <xdr:colOff>27214</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
@@ -10141,7 +10141,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10885714" y="498930"/>
-          <a:ext cx="4826000" cy="2748641"/>
+          <a:ext cx="4426857" cy="2748641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11862,12 +11862,14 @@
       <c r="F3" s="3">
         <v>-10</v>
       </c>
-      <c r="G3" s="3">
-        <v>5000</v>
-      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
+      <c r="I3" s="3">
+        <v>3</v>
+      </c>
+      <c r="J3" s="3">
+        <v>10</v>
+      </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B0BEC2-B169-4F40-A0DC-06CF86F0024A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4165D0BA-76A5-DE41-B428-E4428D9DDA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24840" yWindow="5860" windowWidth="37700" windowHeight="20620" activeTab="11" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="31620" yWindow="5880" windowWidth="37700" windowHeight="20620" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -1168,19 +1168,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1364,7 +1364,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>40</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>90</c:v>
@@ -7820,7 +7820,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>6.67</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>-10</c:v>
@@ -10783,11 +10783,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
@@ -11854,7 +11854,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>6.67</v>
       </c>
       <c r="E3" s="3">
         <v>10</v>
@@ -11865,10 +11865,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -13096,36 +13096,36 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="47" t="s">
+      <c r="L7" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47" t="s">
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="47"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="47" t="s">
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="48"/>
+      <c r="V7" s="48"/>
+      <c r="W7" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="X7" s="47"/>
+      <c r="X7" s="48"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
@@ -13209,16 +13209,16 @@
         <v>177</v>
       </c>
       <c r="C9" s="3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E9" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -13993,74 +13993,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="D4" s="49" t="s">
+      <c r="B4" s="51"/>
+      <c r="D4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="G4" s="49" t="s">
+      <c r="E4" s="51"/>
+      <c r="G4" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="49"/>
-      <c r="J4" s="49" t="s">
+      <c r="H4" s="51"/>
+      <c r="J4" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="49"/>
-      <c r="M4" s="49" t="s">
+      <c r="K4" s="51"/>
+      <c r="M4" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="49"/>
-      <c r="P4" s="49" t="s">
+      <c r="N4" s="51"/>
+      <c r="P4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="51"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="49" t="s">
+      <c r="S4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="49"/>
+      <c r="T4" s="51"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="49" t="s">
+      <c r="V4" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="49"/>
+      <c r="W4" s="51"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="49" t="s">
+      <c r="Y4" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="49"/>
+      <c r="Z4" s="51"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="49" t="s">
+      <c r="AB4" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="49"/>
-      <c r="AE4" s="49" t="s">
+      <c r="AC4" s="51"/>
+      <c r="AE4" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="AF4" s="49"/>
+      <c r="AF4" s="51"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="49" t="s">
+      <c r="AH4" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="AI4" s="49"/>
+      <c r="AI4" s="51"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="49" t="s">
+      <c r="AK4" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="AL4" s="49"/>
+      <c r="AL4" s="51"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="49" t="s">
+      <c r="AN4" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="AO4" s="49"/>
+      <c r="AO4" s="51"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="49" t="s">
+      <c r="AQ4" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="AR4" s="49"/>
+      <c r="AR4" s="51"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -14163,89 +14163,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="50" t="str">
+      <c r="A6" s="49" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="D6" s="50" t="str">
+      <c r="B6" s="50"/>
+      <c r="D6" s="49" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="51"/>
-      <c r="G6" s="50" t="str">
+      <c r="E6" s="50"/>
+      <c r="G6" s="49" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="51"/>
-      <c r="J6" s="50" t="str">
+      <c r="H6" s="50"/>
+      <c r="J6" s="49" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="51"/>
-      <c r="M6" s="50" t="str">
+      <c r="K6" s="50"/>
+      <c r="M6" s="49" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="51"/>
-      <c r="P6" s="50" t="str">
+      <c r="N6" s="50"/>
+      <c r="P6" s="49" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="51"/>
+      <c r="Q6" s="50"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="50" t="str">
+      <c r="S6" s="49" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="51"/>
+      <c r="T6" s="50"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="50" t="str">
+      <c r="V6" s="49" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="51"/>
+      <c r="W6" s="50"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="50" t="str">
+      <c r="Y6" s="49" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="51"/>
+      <c r="Z6" s="50"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="50" t="str">
+      <c r="AB6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="51"/>
-      <c r="AE6" s="50" t="str">
+      <c r="AC6" s="50"/>
+      <c r="AE6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="51"/>
+      <c r="AF6" s="50"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="50" t="str">
+      <c r="AH6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="51"/>
+      <c r="AI6" s="50"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="50" t="str">
+      <c r="AK6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="51"/>
+      <c r="AL6" s="50"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="50" t="str">
+      <c r="AN6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="51"/>
+      <c r="AO6" s="50"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="50" t="str">
+      <c r="AQ6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="51"/>
+      <c r="AR6" s="50"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -14437,7 +14437,7 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B10" s="3">
         <v>20</v>
@@ -15165,36 +15165,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
     <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="AH6:AI6"/>
     <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AN6:AO6"/>
     <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15232,74 +15232,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="D4" s="49" t="s">
+      <c r="B4" s="51"/>
+      <c r="D4" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="G4" s="49" t="s">
+      <c r="E4" s="51"/>
+      <c r="G4" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="49"/>
-      <c r="J4" s="49" t="s">
+      <c r="H4" s="51"/>
+      <c r="J4" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="K4" s="49"/>
-      <c r="M4" s="49" t="s">
+      <c r="K4" s="51"/>
+      <c r="M4" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="49"/>
-      <c r="P4" s="49" t="s">
+      <c r="N4" s="51"/>
+      <c r="P4" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="51"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="49" t="s">
+      <c r="S4" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="T4" s="49"/>
+      <c r="T4" s="51"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="49" t="s">
+      <c r="V4" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="W4" s="49"/>
+      <c r="W4" s="51"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="49" t="s">
+      <c r="Y4" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="Z4" s="49"/>
+      <c r="Z4" s="51"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="49" t="s">
+      <c r="AB4" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="AC4" s="49"/>
-      <c r="AE4" s="49" t="s">
+      <c r="AC4" s="51"/>
+      <c r="AE4" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="AF4" s="49"/>
+      <c r="AF4" s="51"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="49" t="s">
+      <c r="AH4" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="AI4" s="49"/>
+      <c r="AI4" s="51"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="49" t="s">
+      <c r="AK4" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="AL4" s="49"/>
+      <c r="AL4" s="51"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="49" t="s">
+      <c r="AN4" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="AO4" s="49"/>
+      <c r="AO4" s="51"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="49" t="s">
+      <c r="AQ4" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="AR4" s="49"/>
+      <c r="AR4" s="51"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
@@ -16388,14 +16388,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AQ4:AR4"/>
@@ -16412,12 +16410,14 @@
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4165D0BA-76A5-DE41-B428-E4428D9DDA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D3259B-BF8E-1847-BCA0-05E048EDED44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31620" yWindow="5880" windowWidth="37700" windowHeight="20620" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="22760" yWindow="1560" windowWidth="42700" windowHeight="22800" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="182">
   <si>
     <t>X</t>
   </si>
@@ -696,15 +696,9 @@
     <t>Polygon #15</t>
   </si>
   <si>
-    <t>label</t>
-  </si>
-  <si>
     <t>H</t>
   </si>
   <si>
-    <t>theta</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -714,13 +708,47 @@
     <t>I</t>
   </si>
   <si>
-    <t>Required for LEM only</t>
-  </si>
-  <si>
-    <t>Optional</t>
-  </si>
-  <si>
     <t xml:space="preserve">Polygons coordinates can be input in CW or CCW order. </t>
+  </si>
+  <si>
+    <t>Vcap</t>
+  </si>
+  <si>
+    <t>Mcap</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>q</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p</t>
+    </r>
+  </si>
+  <si>
+    <t>LEM only</t>
+  </si>
+  <si>
+    <t>LEM &amp; FEM</t>
+  </si>
+  <si>
+    <t>FEM only</t>
   </si>
   <si>
     <t>soil</t>
@@ -733,7 +761,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -856,6 +884,13 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Symbol"/>
+      <charset val="2"/>
     </font>
   </fonts>
   <fills count="17">
@@ -1042,7 +1077,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1164,10 +1199,12 @@
     <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1207,11 +1244,68 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -8290,7 +8384,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000039-E198-1942-8CC0-5F5B615D56D7}"/>
+                <c16:uniqueId val="{00000039-9273-8E45-8E0C-DF8E6C08CDD2}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8438,673 +8532,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000050-A2F6-274C-9E15-3D60CC318540}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="87"/>
-          <c:order val="87"/>
-          <c:tx>
-            <c:v>Pile #11</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:schemeClr val="accent4">
-                      <a:lumMod val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003B-E198-1942-8CC0-5F5B615D56D7}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(piles!$C$13,piles!$E$13)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(piles!$D$13,piles!$F$13)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000051-A2F6-274C-9E15-3D60CC318540}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="88"/>
-          <c:order val="88"/>
-          <c:tx>
-            <c:v>Pile #12</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(piles!$C$14,piles!$E$14)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(piles!$D$14,piles!$F$14)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000052-A2F6-274C-9E15-3D60CC318540}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="89"/>
-          <c:order val="89"/>
-          <c:tx>
-            <c:v>Pile #13</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(piles!$C$15,piles!$E$15)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(piles!$D$15,piles!$F$15)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000053-A2F6-274C-9E15-3D60CC318540}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="90"/>
-          <c:order val="90"/>
-          <c:tx>
-            <c:v>Pile #14</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="70000"/>
-                    <a:lumOff val="30000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(piles!$C$16,piles!$E$16)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(piles!$D$16,piles!$F$16)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000054-A2F6-274C-9E15-3D60CC318540}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="91"/>
-          <c:order val="91"/>
-          <c:tx>
-            <c:v>Pile #15</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="70000"/>
-                    <a:lumOff val="30000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(piles!$C$17,piles!$E$17)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(piles!$D$17,piles!$F$17)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000055-A2F6-274C-9E15-3D60CC318540}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="92"/>
-          <c:order val="92"/>
-          <c:tx>
-            <c:v>Pile #16</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="70000"/>
-                    <a:lumOff val="30000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(piles!$C$18,piles!$E$18)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(piles!$D$18,piles!$F$18)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000056-A2F6-274C-9E15-3D60CC318540}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="93"/>
-          <c:order val="93"/>
-          <c:tx>
-            <c:v>Pile #17</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="70000"/>
-                    <a:lumOff val="30000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(piles!$C$19,piles!$E$19)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(piles!$D$19,piles!$F$19)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000057-A2F6-274C-9E15-3D60CC318540}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="94"/>
-          <c:order val="94"/>
-          <c:tx>
-            <c:v>Pile #18</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5">
-                    <a:lumMod val="70000"/>
-                    <a:lumOff val="30000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(piles!$C$20,piles!$E$20)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(piles!$D$20,piles!$F$20)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000058-A2F6-274C-9E15-3D60CC318540}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="95"/>
-          <c:order val="95"/>
-          <c:tx>
-            <c:v>Pile #19</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="70000"/>
-                    <a:lumOff val="30000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(piles!$C$21,piles!$E$21)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(piles!$D$21,piles!$F$21)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000059-A2F6-274C-9E15-3D60CC318540}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="96"/>
-          <c:order val="96"/>
-          <c:tx>
-            <c:v>Pile #20</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="70000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(piles!$C$22,piles!$E$22)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(piles!$D$22,piles!$F$22)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000005A-A2F6-274C-9E15-3D60CC318540}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9932,13 +9359,13 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>553357</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>99787</xdr:rowOff>
+      <xdr:rowOff>99788</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>780143</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>54428</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>181429</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9953,8 +9380,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9180286" y="498930"/>
-          <a:ext cx="4354286" cy="2748641"/>
+          <a:off x="9180286" y="498931"/>
+          <a:ext cx="4354286" cy="1877784"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10002,20 +9429,14 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
-        </a:p>
-        <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
             <a:t>Tmax</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = maximum tensile strength of reinforcement material. </a:t>
+            <a:t> = maximum tensile strength (per unit width) of reinforcement material. </a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
         </a:p>
         <a:p>
           <a:r>
@@ -10024,11 +9445,8 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = residual strenth of reinfocement material.</a:t>
+            <a:t> = residual strenth (per unit width) of reinfocement material.</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
         </a:p>
         <a:p>
           <a:r>
@@ -10043,9 +9461,6 @@
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
             <a:t> length or length required to generate full frictional resistance on end corresponding to point 1.</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
         </a:p>
         <a:p>
           <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
@@ -10079,20 +9494,31 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
-        </a:p>
-        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
             <a:t>E</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = modulus of elasticity of reinforcement material</a:t>
+            <a:t> = Young's modulus of reinforcement material (force/length^2)</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
         </a:p>
         <a:p>
           <a:r>
@@ -10101,7 +9527,7 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = cross-sectional area (per unit width) of reinforcement material </a:t>
+            <a:t> = cross-sectional area (per unit width) of reinforcement material.</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
@@ -10116,16 +9542,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>553357</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>99787</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>290285</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>18144</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>27214</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>54428</xdr:rowOff>
+      <xdr:colOff>680357</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10140,8 +9566,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10885714" y="498930"/>
-          <a:ext cx="4426857" cy="2748641"/>
+          <a:off x="12273642" y="217715"/>
+          <a:ext cx="3156858" cy="1841499"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10189,9 +9615,6 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
-        </a:p>
-        <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
             <a:t>H</a:t>
@@ -10202,12 +9625,15 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
-        </a:p>
-        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:latin typeface="Symbol" pitchFamily="2" charset="2"/>
+            </a:rPr>
+            <a:t>q</a:t>
+          </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>theta</a:t>
+            <a:t>p</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
@@ -10223,11 +9649,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Force angle from horizontal in degrees (default 0°; positive = upward)</a:t>
+            <a:t>Force angle from horizontal in degrees (degrees)</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
         </a:p>
         <a:p>
           <a:r>
@@ -10248,11 +9671,29 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Pile diameter.</a:t>
+            <a:t>Pile diameter</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (ft or m)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
@@ -10282,11 +9723,8 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>.</a:t>
+            <a:t> (ft or m)</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
         </a:p>
         <a:p>
           <a:r>
@@ -10295,11 +9733,8 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = Young's modulus of pile material</a:t>
+            <a:t> = Young's modulus of pile material (force/lengh^2)</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
         </a:p>
         <a:p>
           <a:r>
@@ -10320,43 +9755,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Moment of inertia (computed from</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> D</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ar-AE" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>if omitted)</a:t>
+            <a:t>Moment of inertia (length^4)</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
             <a:solidFill>
@@ -10369,9 +9768,6 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
-        </a:p>
-        <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
             <a:t>Area</a:t>
@@ -10390,10 +9786,12 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Cross-sectional area (computed from</a:t>
+            <a:t>Cross-sectional area (length^2)</a:t>
           </a:r>
+        </a:p>
+        <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -10402,10 +9800,10 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> D</a:t>
+            <a:t>Vcap</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ar-AE" sz="1100" b="0" i="0">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -10414,10 +9812,10 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> </a:t>
+            <a:t> = Shear</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -10426,7 +9824,33 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>if omitted)</a:t>
+            <a:t> capacity of pile (force)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Mcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Moment capacity of pile (force x length)</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
@@ -11433,9 +10857,10 @@
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
@@ -11470,7 +10895,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -11485,7 +10910,7 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -11500,7 +10925,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -11515,7 +10940,7 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -11530,7 +10955,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -11545,7 +10970,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -11560,7 +10985,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -11575,7 +11000,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -11590,7 +11015,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -11605,7 +11030,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -11620,7 +11045,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -11635,7 +11060,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -11649,8 +11074,12 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M14" s="31"/>
+      <c r="N14" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -11664,8 +11093,12 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M15" s="34"/>
+      <c r="N15" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -11680,7 +11113,7 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -11695,7 +11128,7 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -11710,7 +11143,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -11724,12 +11157,8 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -11743,12 +11172,8 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -11763,7 +11188,7 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -11778,11 +11203,11 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
@@ -11794,20 +11219,21 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C542BD7-5686-4248-AC02-D49DB39A8FC0}">
-  <dimension ref="A2:P25"/>
+  <dimension ref="A2:R15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
-    <col min="3" max="13" width="10.83203125" style="1"/>
+    <col min="3" max="15" width="10.83203125" style="1"/>
+    <col min="16" max="16" width="3.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>103</v>
@@ -11822,33 +11248,39 @@
         <v>106</v>
       </c>
       <c r="G2" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="J2" s="32" t="s">
         <v>170</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>172</v>
       </c>
       <c r="K2" s="33" t="s">
         <v>101</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M2" s="33" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N2" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="O2" s="46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C3" s="3">
         <v>10</v>
@@ -11873,8 +11305,14 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N3" s="3">
+        <v>25000</v>
+      </c>
+      <c r="O3" s="3">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -11890,8 +11328,10 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -11907,8 +11347,10 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -11924,8 +11366,10 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -11941,8 +11385,10 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -11958,8 +11404,10 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -11975,8 +11423,10 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -11992,8 +11442,10 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -12009,8 +11461,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -12026,196 +11480,30 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="O19" s="46"/>
-      <c r="P19" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="Q12" s="60"/>
+      <c r="R12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q13" s="31"/>
+      <c r="R13" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13206,7 +12494,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C9" s="3">
         <v>120</v>
@@ -13913,33 +13201,38 @@
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="R7:V7"/>
   </mergeCells>
-  <conditionalFormatting sqref="F9:F50">
-    <cfRule type="expression" dxfId="8" priority="1">
-      <formula>$D9="cp"</formula>
+  <conditionalFormatting sqref="F10:F50">
+    <cfRule type="expression" dxfId="16" priority="4">
+      <formula>$D10="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:H50">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:J50">
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="14" priority="5">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9:N50">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="13" priority="7">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:O50">
-    <cfRule type="expression" dxfId="4" priority="14">
+    <cfRule type="expression" dxfId="12" priority="14">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:Q50">
-    <cfRule type="expression" dxfId="3" priority="9">
+    <cfRule type="expression" dxfId="11" priority="9">
+      <formula>$D9="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15228,7 +14521,7 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -16783,19 +16076,24 @@
       <c r="N16" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E3:E42">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>OR($D3="Intercept", $D3="Radius")</formula>
+  <conditionalFormatting sqref="E4:E42">
+    <cfRule type="expression" dxfId="10" priority="4">
+      <formula>OR($D4="Intercept", $D4="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G42">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>OR($D3="Depth",$D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H42">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>OR($D3="Depth",$D3="Intercept")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D3259B-BF8E-1847-BCA0-05E048EDED44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC80A1D-6F0F-7946-B56C-42AA61D9EA7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22760" yWindow="1560" windowWidth="42700" windowHeight="22800" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="14000" yWindow="2020" windowWidth="42700" windowHeight="22800" activeTab="11" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -11302,7 +11302,9 @@
       <c r="J3" s="3">
         <v>6</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>518400000</v>
+      </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3">
@@ -12524,8 +12526,12 @@
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="W9" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="3">

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/fem/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC80A1D-6F0F-7946-B56C-42AA61D9EA7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD98301-3702-904A-BF7A-4A97D6785FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14000" yWindow="2020" windowWidth="42700" windowHeight="22800" activeTab="11" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="25040" yWindow="2500" windowWidth="42700" windowHeight="22800" activeTab="11" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="183">
   <si>
     <t>X</t>
   </si>
@@ -749,6 +749,9 @@
   </si>
   <si>
     <t>FEM only</t>
+  </si>
+  <si>
+    <t>Fixity</t>
   </si>
   <si>
     <t>soil</t>
@@ -1205,6 +1208,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1244,23 +1248,15 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -9542,16 +9538,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>290285</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>18144</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>680357</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>9071</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9566,8 +9562,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12273642" y="217715"/>
-          <a:ext cx="3156858" cy="1841499"/>
+          <a:off x="13099142" y="217715"/>
+          <a:ext cx="3156858" cy="1986642"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9851,6 +9847,32 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:t> = Moment capacity of pile (force x length)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Fixity</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile head status (fixed for free)</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
@@ -10207,11 +10229,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
@@ -10370,36 +10392,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="58" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="F2" s="57" t="s">
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="F2" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="J2" s="57" t="s">
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="J2" s="58" t="s">
         <v>147</v>
       </c>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="N2" s="57" t="s">
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="N2" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="R2" s="57" t="s">
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="R2" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="V2" s="57" t="s">
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="V2" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
+      <c r="W2" s="58"/>
+      <c r="X2" s="58"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -11219,16 +11241,16 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C542BD7-5686-4248-AC02-D49DB39A8FC0}">
-  <dimension ref="A2:R15"/>
+  <dimension ref="A2:Z15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
-    <col min="3" max="15" width="10.83203125" style="1"/>
-    <col min="16" max="16" width="3.83203125" customWidth="1"/>
+    <col min="3" max="16" width="10.83203125" style="1"/>
+    <col min="17" max="17" width="3.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
@@ -11274,13 +11296,19 @@
       <c r="O2" s="46" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P2" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C3" s="3">
         <v>10</v>
@@ -11313,8 +11341,14 @@
       <c r="O3" s="3">
         <v>40000</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -11332,8 +11366,9 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -11351,8 +11386,9 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P5" s="3"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -11370,8 +11406,9 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P6" s="3"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -11389,8 +11426,9 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P7" s="3"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -11408,8 +11446,9 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -11427,8 +11466,9 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -11446,8 +11486,9 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -11465,8 +11506,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -11484,30 +11526,36 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
-      <c r="Q12" s="60"/>
-      <c r="R12" t="s">
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="R13" s="47"/>
+      <c r="S13" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="Q13" s="31"/>
-      <c r="R13" s="9" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="9" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="31"/>
+      <c r="S14" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="9" t="s">
+        <v>179</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{BD18340F-2DC3-724E-BE00-EA96ECBB898C}">
+      <formula1>$Z$2:$Z$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -11527,34 +11575,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="E2" s="54" t="s">
+      <c r="C2" s="59"/>
+      <c r="E2" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="F2" s="54"/>
-      <c r="H2" s="54" t="s">
+      <c r="F2" s="55"/>
+      <c r="H2" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="I2" s="54"/>
-      <c r="K2" s="54" t="s">
+      <c r="I2" s="55"/>
+      <c r="K2" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="54"/>
-      <c r="N2" s="54" t="s">
+      <c r="L2" s="55"/>
+      <c r="N2" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="O2" s="54"/>
-      <c r="Q2" s="54" t="s">
+      <c r="O2" s="55"/>
+      <c r="Q2" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="R2" s="54"/>
+      <c r="R2" s="55"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
       <c r="E3" s="37" t="s">
         <v>95</v>
       </c>
@@ -11921,34 +11969,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="E2" s="55" t="s">
+      <c r="C2" s="60"/>
+      <c r="E2" s="56" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="55"/>
-      <c r="H2" s="55" t="s">
+      <c r="F2" s="56"/>
+      <c r="H2" s="56" t="s">
         <v>141</v>
       </c>
-      <c r="I2" s="55"/>
-      <c r="K2" s="55" t="s">
+      <c r="I2" s="56"/>
+      <c r="K2" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="N2" s="55" t="s">
+      <c r="L2" s="56"/>
+      <c r="N2" s="56" t="s">
         <v>143</v>
       </c>
-      <c r="O2" s="55"/>
-      <c r="Q2" s="55" t="s">
+      <c r="O2" s="56"/>
+      <c r="Q2" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="R2" s="55"/>
+      <c r="R2" s="56"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
       <c r="E3" s="39" t="s">
         <v>95</v>
       </c>
@@ -12386,36 +12434,36 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="48" t="s">
+      <c r="L7" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48" t="s">
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="S7" s="48"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
-      <c r="V7" s="48"/>
-      <c r="W7" s="48" t="s">
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="X7" s="48"/>
+      <c r="X7" s="49"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
@@ -12496,7 +12544,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C9" s="3">
         <v>120</v>
@@ -13208,37 +13256,62 @@
     <mergeCell ref="R7:V7"/>
   </mergeCells>
   <conditionalFormatting sqref="F10:F50">
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="15" priority="9">
       <formula>$D10="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9:H50">
-    <cfRule type="expression" dxfId="15" priority="3">
+  <conditionalFormatting sqref="G10:H50">
+    <cfRule type="expression" dxfId="14" priority="8">
+      <formula>$D10="mc"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10:J50">
+    <cfRule type="expression" dxfId="13" priority="10">
+      <formula>$D10="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N10:N50">
+    <cfRule type="expression" dxfId="12" priority="12">
+      <formula>$D10="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O10:O50">
+    <cfRule type="expression" dxfId="11" priority="19">
+      <formula>$D10="mc"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P10:Q50">
+    <cfRule type="expression" dxfId="10" priority="14">
+      <formula>$D10="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>$D9="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9:H9">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:J50">
-    <cfRule type="expression" dxfId="14" priority="5">
+  <conditionalFormatting sqref="I9:J9">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N9:N50">
-    <cfRule type="expression" dxfId="13" priority="7">
+  <conditionalFormatting sqref="N9">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O9:O50">
-    <cfRule type="expression" dxfId="12" priority="14">
+  <conditionalFormatting sqref="O9">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P9:Q50">
-    <cfRule type="expression" dxfId="11" priority="9">
-      <formula>$D9="cp"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="P9:Q9">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13292,74 +13365,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="D4" s="51" t="s">
+      <c r="B4" s="52"/>
+      <c r="D4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="G4" s="51" t="s">
+      <c r="E4" s="52"/>
+      <c r="G4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="51"/>
-      <c r="J4" s="51" t="s">
+      <c r="H4" s="52"/>
+      <c r="J4" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="51"/>
-      <c r="M4" s="51" t="s">
+      <c r="K4" s="52"/>
+      <c r="M4" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="51"/>
-      <c r="P4" s="51" t="s">
+      <c r="N4" s="52"/>
+      <c r="P4" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="51"/>
+      <c r="Q4" s="52"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="51" t="s">
+      <c r="S4" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="51"/>
+      <c r="T4" s="52"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="51" t="s">
+      <c r="V4" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="51"/>
+      <c r="W4" s="52"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="51" t="s">
+      <c r="Y4" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="51"/>
+      <c r="Z4" s="52"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="51" t="s">
+      <c r="AB4" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="51"/>
-      <c r="AE4" s="51" t="s">
+      <c r="AC4" s="52"/>
+      <c r="AE4" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="AF4" s="51"/>
+      <c r="AF4" s="52"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="51" t="s">
+      <c r="AH4" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="AI4" s="51"/>
+      <c r="AI4" s="52"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="51" t="s">
+      <c r="AK4" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="AL4" s="51"/>
+      <c r="AL4" s="52"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="51" t="s">
+      <c r="AN4" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="AO4" s="51"/>
+      <c r="AO4" s="52"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="51" t="s">
+      <c r="AQ4" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="AR4" s="51"/>
+      <c r="AR4" s="52"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -13462,89 +13535,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="49" t="str">
+      <c r="A6" s="50" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="D6" s="49" t="str">
+      <c r="B6" s="51"/>
+      <c r="D6" s="50" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="50"/>
-      <c r="G6" s="49" t="str">
+      <c r="E6" s="51"/>
+      <c r="G6" s="50" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="50"/>
-      <c r="J6" s="49" t="str">
+      <c r="H6" s="51"/>
+      <c r="J6" s="50" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="50"/>
-      <c r="M6" s="49" t="str">
+      <c r="K6" s="51"/>
+      <c r="M6" s="50" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="50"/>
-      <c r="P6" s="49" t="str">
+      <c r="N6" s="51"/>
+      <c r="P6" s="50" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="50"/>
+      <c r="Q6" s="51"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="49" t="str">
+      <c r="S6" s="50" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="50"/>
+      <c r="T6" s="51"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="49" t="str">
+      <c r="V6" s="50" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="50"/>
+      <c r="W6" s="51"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="49" t="str">
+      <c r="Y6" s="50" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="50"/>
+      <c r="Z6" s="51"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="49" t="str">
+      <c r="AB6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="50"/>
-      <c r="AE6" s="49" t="str">
+      <c r="AC6" s="51"/>
+      <c r="AE6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="50"/>
+      <c r="AF6" s="51"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="49" t="str">
+      <c r="AH6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="50"/>
+      <c r="AI6" s="51"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="49" t="str">
+      <c r="AK6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="50"/>
+      <c r="AL6" s="51"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="49" t="str">
+      <c r="AN6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="50"/>
+      <c r="AO6" s="51"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="49" t="str">
+      <c r="AQ6" s="50" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="50"/>
+      <c r="AR6" s="51"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -14531,74 +14604,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="52" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="D4" s="51" t="s">
+      <c r="B4" s="52"/>
+      <c r="D4" s="52" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="G4" s="51" t="s">
+      <c r="E4" s="52"/>
+      <c r="G4" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="51"/>
-      <c r="J4" s="51" t="s">
+      <c r="H4" s="52"/>
+      <c r="J4" s="52" t="s">
         <v>156</v>
       </c>
-      <c r="K4" s="51"/>
-      <c r="M4" s="51" t="s">
+      <c r="K4" s="52"/>
+      <c r="M4" s="52" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="51"/>
-      <c r="P4" s="51" t="s">
+      <c r="N4" s="52"/>
+      <c r="P4" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="Q4" s="51"/>
+      <c r="Q4" s="52"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="51" t="s">
+      <c r="S4" s="52" t="s">
         <v>159</v>
       </c>
-      <c r="T4" s="51"/>
+      <c r="T4" s="52"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="51" t="s">
+      <c r="V4" s="52" t="s">
         <v>160</v>
       </c>
-      <c r="W4" s="51"/>
+      <c r="W4" s="52"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="51" t="s">
+      <c r="Y4" s="52" t="s">
         <v>161</v>
       </c>
-      <c r="Z4" s="51"/>
+      <c r="Z4" s="52"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="51" t="s">
+      <c r="AB4" s="52" t="s">
         <v>162</v>
       </c>
-      <c r="AC4" s="51"/>
-      <c r="AE4" s="51" t="s">
+      <c r="AC4" s="52"/>
+      <c r="AE4" s="52" t="s">
         <v>163</v>
       </c>
-      <c r="AF4" s="51"/>
+      <c r="AF4" s="52"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="51" t="s">
+      <c r="AH4" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="AI4" s="51"/>
+      <c r="AI4" s="52"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="51" t="s">
+      <c r="AK4" s="52" t="s">
         <v>165</v>
       </c>
-      <c r="AL4" s="51"/>
+      <c r="AL4" s="52"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="51" t="s">
+      <c r="AN4" s="52" t="s">
         <v>166</v>
       </c>
-      <c r="AO4" s="51"/>
+      <c r="AO4" s="52"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="51" t="s">
+      <c r="AQ4" s="52" t="s">
         <v>167</v>
       </c>
-      <c r="AR4" s="51"/>
+      <c r="AR4" s="52"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
@@ -14701,89 +14774,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="str">
+      <c r="A6" s="53" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="D6" s="52" t="str">
+      <c r="B6" s="54"/>
+      <c r="D6" s="53" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="53"/>
-      <c r="G6" s="52" t="str">
+      <c r="E6" s="54"/>
+      <c r="G6" s="53" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="53"/>
-      <c r="J6" s="52" t="str">
+      <c r="H6" s="54"/>
+      <c r="J6" s="53" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="53"/>
-      <c r="M6" s="52" t="str">
+      <c r="K6" s="54"/>
+      <c r="M6" s="53" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="53"/>
-      <c r="P6" s="52" t="str">
+      <c r="N6" s="54"/>
+      <c r="P6" s="53" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="53"/>
+      <c r="Q6" s="54"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="52" t="str">
+      <c r="S6" s="53" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="53"/>
+      <c r="T6" s="54"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="52" t="str">
+      <c r="V6" s="53" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="53"/>
+      <c r="W6" s="54"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="52" t="str">
+      <c r="Y6" s="53" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="53"/>
+      <c r="Z6" s="54"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="52" t="str">
+      <c r="AB6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="53"/>
-      <c r="AE6" s="52" t="str">
+      <c r="AC6" s="54"/>
+      <c r="AE6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="53"/>
+      <c r="AF6" s="54"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="52" t="str">
+      <c r="AH6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="53"/>
+      <c r="AI6" s="54"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="52" t="str">
+      <c r="AK6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="53"/>
+      <c r="AL6" s="54"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="52" t="str">
+      <c r="AN6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="53"/>
+      <c r="AO6" s="54"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="52" t="str">
+      <c r="AQ6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="53"/>
+      <c r="AR6" s="54"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -15732,14 +15805,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="D2" s="55" t="s">
+      <c r="B2" s="55"/>
+      <c r="D2" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="55"/>
+      <c r="E2" s="56"/>
       <c r="G2" s="24" t="s">
         <v>83</v>
       </c>
@@ -16083,17 +16156,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E4:E42">
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>OR($D4="Intercept", $D4="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G42">
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>OR($D3="Depth",$D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H42">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>OR($D3="Depth",$D3="Intercept")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16291,36 +16364,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="F2" s="56" t="s">
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="F2" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="J2" s="56" t="s">
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="J2" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="N2" s="56" t="s">
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="N2" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="R2" s="56" t="s">
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="R2" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="V2" s="56" t="s">
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="V2" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="W2" s="56"/>
-      <c r="X2" s="56"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/fem/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD98301-3702-904A-BF7A-4A97D6785FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31A0517-52BD-804D-9055-31F3F3538037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25040" yWindow="2500" windowWidth="42700" windowHeight="22800" activeTab="11" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="31660" yWindow="2660" windowWidth="36220" windowHeight="22300" activeTab="11" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="183">
   <si>
     <t>X</t>
   </si>
@@ -1252,56 +1252,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
@@ -1454,10 +1405,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7895,10 +7846,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7910,7 +7861,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6.67</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>-10</c:v>
@@ -7970,6 +7921,12 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -7979,6 +7936,12 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-10</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -11311,13 +11274,13 @@
         <v>182</v>
       </c>
       <c r="C3" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3">
-        <v>6.67</v>
+        <v>5</v>
       </c>
       <c r="E3" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" s="3">
         <v>-10</v>
@@ -11325,7 +11288,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="3">
         <v>6</v>
@@ -11336,10 +11299,10 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3">
-        <v>25000</v>
+        <v>46000</v>
       </c>
       <c r="O3" s="3">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>40</v>
@@ -11350,23 +11313,48 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="3">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-10</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="I4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3">
+        <v>6</v>
+      </c>
+      <c r="K4" s="3">
+        <v>518400000</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
+      <c r="N4" s="3">
+        <v>46000</v>
+      </c>
+      <c r="O4" s="3">
+        <v>60000</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
@@ -12556,7 +12544,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -12575,10 +12563,10 @@
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="X9" s="3">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
@@ -13255,63 +13243,33 @@
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="R7:V7"/>
   </mergeCells>
-  <conditionalFormatting sqref="F10:F50">
-    <cfRule type="expression" dxfId="15" priority="9">
-      <formula>$D10="cp"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G10:H50">
-    <cfRule type="expression" dxfId="14" priority="8">
-      <formula>$D10="mc"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I10:J50">
-    <cfRule type="expression" dxfId="13" priority="10">
-      <formula>$D10="cp"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N10:N50">
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>$D10="cp"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O10:O50">
-    <cfRule type="expression" dxfId="11" priority="19">
-      <formula>$D10="mc"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P10:Q50">
-    <cfRule type="expression" dxfId="10" priority="14">
-      <formula>$D10="cp"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="6" priority="1">
+  <conditionalFormatting sqref="F9:F50">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9:H9">
-    <cfRule type="expression" dxfId="5" priority="2">
+  <conditionalFormatting sqref="G9:H50">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:J9">
-    <cfRule type="expression" dxfId="4" priority="3">
+  <conditionalFormatting sqref="I9:J50">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N9">
-    <cfRule type="expression" dxfId="3" priority="4">
+  <conditionalFormatting sqref="N9:N50">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O9">
-    <cfRule type="expression" dxfId="2" priority="6">
+  <conditionalFormatting sqref="O9:O50">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P9:Q9">
-    <cfRule type="expression" dxfId="1" priority="5">
+  <conditionalFormatting sqref="P9:Q50">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13809,7 +13767,7 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B10" s="3">
         <v>20</v>
@@ -13853,7 +13811,7 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B11" s="3">
         <v>20</v>
@@ -16155,24 +16113,19 @@
       <c r="N16" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E4:E42">
-    <cfRule type="expression" dxfId="9" priority="4">
-      <formula>OR($D4="Intercept", $D4="Radius")</formula>
+  <conditionalFormatting sqref="E3:E42">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G42">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>OR($D3="Depth",$D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H42">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>OR($D3="Depth",$D3="Intercept")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31A0517-52BD-804D-9055-31F3F3538037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53F4FFA-A72E-9849-8C3B-3C3A51EB7D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31660" yWindow="2660" windowWidth="36220" windowHeight="22300" activeTab="11" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="11520" yWindow="2900" windowWidth="42700" windowHeight="22800" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,9 @@
     <sheet name="dloads (2)" sheetId="13" r:id="rId10"/>
     <sheet name="reinforce" sheetId="12" r:id="rId11"/>
     <sheet name="piles" sheetId="16" r:id="rId12"/>
-    <sheet name="seep bc" sheetId="11" r:id="rId13"/>
-    <sheet name="seep bc (2)" sheetId="14" r:id="rId14"/>
+    <sheet name="lloads" sheetId="17" r:id="rId13"/>
+    <sheet name="seep bc" sheetId="11" r:id="rId14"/>
+    <sheet name="seep bc (2)" sheetId="14" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="crack_depth">main!$D$9</definedName>
@@ -40,7 +41,7 @@
     <definedName name="solution2">mat!#REF!</definedName>
     <definedName name="version">main!$D$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="212">
   <si>
     <t>X</t>
   </si>
@@ -422,9 +423,6 @@
     <t>Piezometric Line 1</t>
   </si>
   <si>
-    <t>Pore presssue (u) options</t>
-  </si>
-  <si>
     <t>u</t>
   </si>
   <si>
@@ -492,12 +490,6 @@
   </si>
   <si>
     <t>Tmax</t>
-  </si>
-  <si>
-    <t>Required for FEM only</t>
-  </si>
-  <si>
-    <t>Required for both LEM and FEM</t>
   </si>
   <si>
     <t>Lp1</t>
@@ -754,17 +746,130 @@
     <t>Fixity</t>
   </si>
   <si>
-    <t>soil</t>
-  </si>
-  <si>
-    <t>pile</t>
+    <t>unsat</t>
+  </si>
+  <si>
+    <t>lf</t>
+  </si>
+  <si>
+    <t>vg</t>
+  </si>
+  <si>
+    <t>linear front model (kr0,h0)</t>
+  </si>
+  <si>
+    <t>van Genuchten model (vb_a, vg_n)</t>
+  </si>
+  <si>
+    <t>Unsat model option</t>
+  </si>
+  <si>
+    <t>vg_a</t>
+  </si>
+  <si>
+    <t>vg_n</t>
+  </si>
+  <si>
+    <t>Pore pressure (u) options</t>
+  </si>
+  <si>
+    <t>pow</t>
+  </si>
+  <si>
+    <t>ru</t>
+  </si>
+  <si>
+    <t>pow_a</t>
+  </si>
+  <si>
+    <t>pow_b</t>
+  </si>
+  <si>
+    <t>pow_c</t>
+  </si>
+  <si>
+    <t>pow_d</t>
+  </si>
+  <si>
+    <t>Appl</t>
+  </si>
+  <si>
+    <t>Tend1</t>
+  </si>
+  <si>
+    <t>Tend2</t>
+  </si>
+  <si>
+    <t>Geosynthetic</t>
+  </si>
+  <si>
+    <t>Tangent</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Nail</t>
+  </si>
+  <si>
+    <t>Axial</t>
+  </si>
+  <si>
+    <t>Passive</t>
+  </si>
+  <si>
+    <t>Tieback</t>
+  </si>
+  <si>
+    <t>Anchor</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>sat</t>
+    </r>
+  </si>
+  <si>
+    <t>Pore pressure ratio (u = ru * sigma_v)</t>
+  </si>
+  <si>
+    <t>Power curve envelope: t = pow_a * (sn + pow_d)^pow_b + pow_c</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Dir</t>
+  </si>
+  <si>
+    <t>Spacing</t>
+  </si>
+  <si>
+    <t>Angle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -894,6 +999,17 @@
       <color theme="0"/>
       <name val="Symbol"/>
       <charset val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="17">
@@ -1080,7 +1196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1209,19 +1325,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1252,7 +1375,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill>
@@ -1271,6 +1394,20 @@
       <fill>
         <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1305,7 +1442,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1398,18 +1563,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>-30</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>80</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1419,18 +1572,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -4164,7 +4305,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$3,reinforce!$D$3)</c:f>
+              <c:f>(reinforce!$C$3,reinforce!$E$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4173,7 +4314,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$3,reinforce!$E$3)</c:f>
+              <c:f>(reinforce!$D$3,reinforce!$F$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4225,7 +4366,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$4,reinforce!$D$4)</c:f>
+              <c:f>(reinforce!$C$4,reinforce!$E$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4234,7 +4375,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$4,reinforce!$C$4,reinforce!$C$4,reinforce!$E$4)</c:f>
+              <c:f>(reinforce!$D$4,reinforce!$D$4,reinforce!$D$4,reinforce!$F$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -4286,7 +4427,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$5,reinforce!$D$5)</c:f>
+              <c:f>(reinforce!$C$5,reinforce!$E$5)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4295,7 +4436,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$5,reinforce!$E$5)</c:f>
+              <c:f>(reinforce!$D$5,reinforce!$F$5)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4347,7 +4488,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$6,reinforce!$D$6)</c:f>
+              <c:f>(reinforce!$C$6,reinforce!$E$6)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4356,7 +4497,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$6,reinforce!$E$6)</c:f>
+              <c:f>(reinforce!$D$6,reinforce!$F$6)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4411,7 +4552,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$7,reinforce!$D$7)</c:f>
+              <c:f>(reinforce!$C$7,reinforce!$E$7)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4420,7 +4561,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$7,reinforce!$E$7)</c:f>
+              <c:f>(reinforce!$D$7,reinforce!$F$7)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4475,7 +4616,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$8,reinforce!$D$8)</c:f>
+              <c:f>(reinforce!$C$8,reinforce!$E$8)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4484,7 +4625,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$8,reinforce!$E$8)</c:f>
+              <c:f>(reinforce!$D$8,reinforce!$F$8)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4539,7 +4680,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$9,reinforce!$D$9)</c:f>
+              <c:f>(reinforce!$C$9,reinforce!$E$9)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4548,7 +4689,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$9,reinforce!$E$9)</c:f>
+              <c:f>(reinforce!$D$9,reinforce!$F$9)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4603,7 +4744,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$10,reinforce!$D$10)</c:f>
+              <c:f>(reinforce!$C$10,reinforce!$E$10)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4612,7 +4753,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$10,reinforce!$E$10)</c:f>
+              <c:f>(reinforce!$D$10,reinforce!$F$10)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4667,7 +4808,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$11,reinforce!$D$11)</c:f>
+              <c:f>(reinforce!$C$11,reinforce!$E$11)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4676,7 +4817,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$11,reinforce!$E$11)</c:f>
+              <c:f>(reinforce!$D$11,reinforce!$F$11)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4731,7 +4872,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$12,reinforce!$D$12)</c:f>
+              <c:f>(reinforce!$C$12,reinforce!$E$12)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4740,7 +4881,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$12,reinforce!$E$12)</c:f>
+              <c:f>(reinforce!$D$12,reinforce!$F$12)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4792,7 +4933,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$13,reinforce!$D$13)</c:f>
+              <c:f>(reinforce!$C$13,reinforce!$E$13)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4801,7 +4942,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$13,reinforce!$E$13)</c:f>
+              <c:f>(reinforce!$D$13,reinforce!$F$13)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4853,7 +4994,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$14,reinforce!$D$14)</c:f>
+              <c:f>(reinforce!$C$14,reinforce!$E$14)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4862,7 +5003,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$14,reinforce!$E$14)</c:f>
+              <c:f>(reinforce!$D$14,reinforce!$F$14)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4917,7 +5058,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$15,reinforce!$D$15)</c:f>
+              <c:f>(reinforce!$C$15,reinforce!$E$15)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4926,7 +5067,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$15,reinforce!$E$15)</c:f>
+              <c:f>(reinforce!$D$15,reinforce!$F$15)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4981,7 +5122,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$16,reinforce!$D$16)</c:f>
+              <c:f>(reinforce!$C$16,reinforce!$E$16)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4990,7 +5131,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$16,reinforce!$E$16)</c:f>
+              <c:f>(reinforce!$D$16,reinforce!$F$16)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5045,7 +5186,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$17,reinforce!$D$17)</c:f>
+              <c:f>(reinforce!$C$17,reinforce!$E$17)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5054,7 +5195,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$17,reinforce!$E$17)</c:f>
+              <c:f>(reinforce!$D$17,reinforce!$F$17)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5109,7 +5250,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$18,reinforce!$D$18)</c:f>
+              <c:f>(reinforce!$C$18,reinforce!$E$18)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5118,7 +5259,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$18,reinforce!$E$18)</c:f>
+              <c:f>(reinforce!$D$18,reinforce!$F$18)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5173,7 +5314,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$19,reinforce!$D$19)</c:f>
+              <c:f>(reinforce!$C$19,reinforce!$E$19)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5182,7 +5323,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$19,reinforce!$E$19)</c:f>
+              <c:f>(reinforce!$D$19,reinforce!$F$19)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5234,7 +5375,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$20,reinforce!$D$20)</c:f>
+              <c:f>(reinforce!$C$20,reinforce!$E$20)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5243,7 +5384,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$20,reinforce!$E$20)</c:f>
+              <c:f>(reinforce!$D$20,reinforce!$F$20)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5295,7 +5436,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$21,reinforce!$D$21)</c:f>
+              <c:f>(reinforce!$C$21,reinforce!$E$21)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5304,7 +5445,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$21,reinforce!$E$21)</c:f>
+              <c:f>(reinforce!$D$21,reinforce!$F$21)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5356,7 +5497,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$22,reinforce!$D$22)</c:f>
+              <c:f>(reinforce!$C$22,reinforce!$E$22)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5365,7 +5506,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$22,reinforce!$E$22)</c:f>
+              <c:f>(reinforce!$D$22,reinforce!$F$22)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -7845,12 +7986,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -7860,12 +7995,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-10</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -7921,12 +8050,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -7936,12 +8059,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-10</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -9315,16 +9432,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>553357</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>99788</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>308429</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>780143</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>181429</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>290286</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>90713</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9339,8 +9456,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9180286" y="498931"/>
-          <a:ext cx="4354286" cy="1877784"/>
+          <a:off x="14895286" y="335643"/>
+          <a:ext cx="3610429" cy="3746499"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9376,119 +9493,122 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
-            <a:t>(x1,</a:t>
+            <a:t>(x1, y1), (x2, y2) </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t> y1), (x2, y2) </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>= endpoints of reinforcement line</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>Tmax</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = maximum tensile strength (per unit width) of reinforcement material. </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>Tres</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = residual strenth (per unit width) of reinfocement material.</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= start and end of reinforcement line</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
-            <a:t>Lp1</a:t>
+            <a:t>Label</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t> = pullout</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> length or length required to generate full frictional resistance on end corresponding to point 1.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1"/>
-            <a:t>Lp2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t> = pullout</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> length or length required to generate full frictional resistance on end corresponding to point 2.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>E</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = Young's modulus of reinforcement material (force/length^2)</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = name used in error messages, summaries, and plots</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Type</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = support preset, fills Dir and Appl: Geosynthetic (Tangent, Active), Nail (Axial, Passive), Tieback (Axial, Active), Anchor (Axial, Active)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Dir</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force direction at the slip surface (LEM only): Tangent = reorients along slip surface (flexible); Axial = along the reinforcement line (rigid). Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS. Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tmax</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = tensile capacity (force/length; or force per element if Spacing is given)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Lp1, Lp2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= pullout length at end 1 / end 2 (0 = fully anchored)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tend1, Tend2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= anchorage/plate/connection capacity at end 1 / end 2 (0 = friction only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Spacing</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = out-of-plane spacing for discrete supports (nails, tiebacks); blank or 1 for geosynthetics</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tres</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = residual capacity after rupture (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = modulus of elasticity of reinforcement (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Area</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = cross-sectional area (per unit width) of reinforcement material.</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -9501,16 +9621,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>290285</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>18144</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>344713</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>181429</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>680357</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>9071</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>607785</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>108855</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9525,8 +9645,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13099142" y="217715"/>
-          <a:ext cx="3156858" cy="1986642"/>
+          <a:off x="14260284" y="181429"/>
+          <a:ext cx="3156858" cy="2521855"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9613,6 +9733,32 @@
         </a:p>
         <a:p>
           <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>D</a:t>
           </a:r>
@@ -9687,6 +9833,71 @@
         </a:p>
         <a:p>
           <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Vcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Shear</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> capacity of pile (force)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Mcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Moment capacity of pile (force x length)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
             <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
             <a:t>E</a:t>
           </a:r>
@@ -9750,70 +9961,6 @@
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Vcap</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> = Shear</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> capacity of pile (force)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Mcap</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> = Moment capacity of pile (force x length)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
             <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -9835,7 +9982,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> = Pile head status (fixed for free)</a:t>
+            <a:t> = Pile head status (fixed or free)</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
@@ -10162,7 +10309,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02E090B-D957-7046-AD33-44E170F709C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FAED0A-C8CC-8343-BA2E-B8E4255891E7}">
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10175,7 +10322,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19" x14ac:dyDescent="0.25">
@@ -10188,15 +10335,15 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
@@ -10212,10 +10359,10 @@
         <v>62.4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -10223,7 +10370,7 @@
         <v>49</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>19</v>
@@ -10237,7 +10384,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
@@ -10252,7 +10399,7 @@
         <v>75</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>21</v>
@@ -10287,10 +10434,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F15" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -10304,18 +10451,18 @@
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="F18" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
@@ -10336,7 +10483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A261BE0-CD66-F942-872D-854CE40C6F7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{028A122E-8CB6-264D-BE4D-4184948E7CD8}">
   <dimension ref="B2:X22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10355,36 +10502,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="F2" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="J2" s="61" t="s">
+        <v>144</v>
+      </c>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="N2" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="F2" s="58" t="s">
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="R2" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="J2" s="58" t="s">
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="V2" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="N2" s="58" t="s">
-        <v>148</v>
-      </c>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="R2" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="V2" s="58" t="s">
-        <v>150</v>
-      </c>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -10836,51 +10983,84 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C4F752-BCE4-AE4E-BC09-D828329F219B}">
-  <dimension ref="A2:N25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37CF166-6531-CC44-B460-D72E6A0F66E6}">
+  <dimension ref="A2:AB25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
-    <col min="2" max="11" width="10.83203125" style="1"/>
-    <col min="12" max="12" width="7.6640625" customWidth="1"/>
+    <col min="2" max="6" width="10.83203125" style="1"/>
+    <col min="7" max="7" width="13.1640625" customWidth="1"/>
+    <col min="10" max="12" width="10.83203125" style="1"/>
+    <col min="16" max="18" width="10.83203125" style="1"/>
+    <col min="19" max="19" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="M2" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="N2" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="O2" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="P2" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q2" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="R2" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="K2" s="33" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="Z2" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -10890,12 +11070,34 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="3" t="str">
+        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
+        <v/>
+      </c>
+      <c r="I3" s="3" t="str">
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
+        <v/>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="Z3" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -10905,12 +11107,28 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I4" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="Z4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -10920,12 +11138,28 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I5" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="Z5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -10935,12 +11169,25 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I6" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -10950,12 +11197,25 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I7" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -10965,12 +11225,34 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I8" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="Z8" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -10980,12 +11262,34 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I9" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="Z9" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -10995,12 +11299,34 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I10" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="Z10" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -11010,12 +11336,34 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I11" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="Z11" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -11025,12 +11373,25 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I12" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -11040,12 +11401,25 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="H13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I13" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -11055,16 +11429,25 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I14" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -11074,16 +11457,25 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="H15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I15" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -11093,12 +11485,25 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I16" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -11108,12 +11513,25 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="H17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I17" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -11123,12 +11541,25 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -11138,12 +11569,25 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="H19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -11153,12 +11597,25 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="H20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I20" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -11168,12 +11625,25 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="H21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I21" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -11183,180 +11653,236 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="H22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I22" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="T23" s="47"/>
+      <c r="U23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="T25" s="34"/>
+      <c r="U25" s="9" t="s">
+        <v>176</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G22" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H22" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I22" xr:uid="{00000000-0002-0000-0A00-000002000000}">
+      <formula1>$AB$2:$AB$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C542BD7-5686-4248-AC02-D49DB39A8FC0}">
-  <dimension ref="A2:Z15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B6221D-E989-B546-ACAF-CEB4607C51A1}">
+  <dimension ref="A2:AA18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
-    <col min="3" max="16" width="10.83203125" style="1"/>
-    <col min="17" max="17" width="3.83203125" customWidth="1"/>
+    <col min="3" max="8" width="10.83203125" style="1"/>
+    <col min="9" max="9" width="14.5" customWidth="1"/>
+    <col min="10" max="17" width="10.83203125" style="1"/>
+    <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="L2" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="M2" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="O2" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="P2" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2" s="45" t="s">
-        <v>176</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="K2" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="L2" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="M2" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="N2" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="O2" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="P2" s="33" t="s">
-        <v>180</v>
+      <c r="Q2" s="33" t="s">
+        <v>177</v>
       </c>
       <c r="Z2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>182</v>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>pile</t>
+        </is>
       </c>
       <c r="C3" s="3">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="E3" s="3">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="F3" s="3">
-        <v>-10</v>
+        <v>-10.0</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3">
-        <v>2</v>
-      </c>
+      <c r="I3" s="3"/>
       <c r="J3" s="3">
-        <v>6</v>
+        <v>2.0</v>
       </c>
       <c r="K3" s="3">
-        <v>518400000</v>
-      </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>46000.0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>60000.0</v>
+      </c>
       <c r="N3" s="3">
-        <v>46000</v>
-      </c>
-      <c r="O3" s="3">
-        <v>60000</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>40</v>
+        <v>518400000.0</v>
+      </c>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
       </c>
       <c r="Z3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>182</v>
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>pile</t>
+        </is>
       </c>
       <c r="C4" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="D4" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="E4" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F4" s="3">
-        <v>-10</v>
+        <v>-10.0</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3">
-        <v>2</v>
-      </c>
+      <c r="I4" s="3"/>
       <c r="J4" s="3">
-        <v>6</v>
+        <v>2.0</v>
       </c>
       <c r="K4" s="3">
-        <v>518400000</v>
-      </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>46000.0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>60000.0</v>
+      </c>
       <c r="N4" s="3">
-        <v>46000</v>
-      </c>
-      <c r="O4" s="3">
-        <v>60000</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+        <v>518400000.0</v>
+      </c>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -11375,8 +11901,9 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q5" s="3"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -11395,8 +11922,9 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -11415,8 +11943,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -11435,8 +11964,9 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -11455,1123 +11985,11 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R13" s="47"/>
-      <c r="S13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="9" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="9" t="s">
-        <v>179</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{BD18340F-2DC3-724E-BE00-EA96ECBB898C}">
-      <formula1>$Z$2:$Z$3</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{847CAF5A-5624-4041-9578-842C28E166A5}">
-  <dimension ref="B2:R24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="7" max="7" width="4" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" customWidth="1"/>
-    <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="16" max="16" width="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="E2" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="F2" s="55"/>
-      <c r="H2" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" s="55"/>
-      <c r="K2" s="55" t="s">
-        <v>135</v>
-      </c>
-      <c r="L2" s="55"/>
-      <c r="N2" s="55" t="s">
-        <v>136</v>
-      </c>
-      <c r="O2" s="55"/>
-      <c r="Q2" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="R2" s="55"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="E3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="F3" s="38"/>
-      <c r="H3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="38"/>
-      <c r="K3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="L3" s="38"/>
-      <c r="N3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="O3" s="38"/>
-      <c r="Q3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="R3" s="38"/>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="R4" s="28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1356292-DB08-1D46-A803-E893EDEE17F7}">
-  <dimension ref="B2:R24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="7" max="7" width="4" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" customWidth="1"/>
-    <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="16" max="16" width="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="60" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="E2" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="F2" s="56"/>
-      <c r="H2" s="56" t="s">
-        <v>141</v>
-      </c>
-      <c r="I2" s="56"/>
-      <c r="K2" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="L2" s="56"/>
-      <c r="N2" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="O2" s="56"/>
-      <c r="Q2" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="R2" s="56"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="E3" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="F3" s="40"/>
-      <c r="H3" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="40"/>
-      <c r="K3" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="L3" s="40"/>
-      <c r="N3" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="O3" s="40"/>
-      <c r="Q3" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="R3" s="40"/>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="R4" s="28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="N2:O2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56CEDAD3-D805-AE4D-9F0D-9E80BF51FF21}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA88A0E-2BF5-FE49-9603-08BE4D91829B}">
-  <dimension ref="A2:X50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="7" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
-    <col min="3" max="9" width="8.5" style="1" customWidth="1"/>
-    <col min="10" max="13" width="8.5" customWidth="1"/>
-    <col min="14" max="17" width="10.83203125" customWidth="1"/>
-    <col min="23" max="23" width="10.83203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C2" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="J2" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="J3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O3" s="14"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="J4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>60</v>
-      </c>
-      <c r="O4" s="14"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O5" s="14"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C7" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="X7" s="49"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="O8" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="P8" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q8" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="R8" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="S8" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="T8" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="U8" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="V8" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="W8" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="X8" s="30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>1</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="3">
-        <v>120</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="3">
-        <v>200</v>
-      </c>
-      <c r="F9" s="3">
-        <v>20</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="X9" s="3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>2</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -12589,17 +12007,1467 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S16" s="47"/>
+      <c r="T16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="31"/>
+      <c r="T17" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S18" s="34"/>
+      <c r="T18" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q12" xr:uid="{BD18340F-2DC3-724E-BE00-EA96ECBB898C}">
+      <formula1>$Z$2:$Z$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I12" xr:uid="{00000000-0002-0000-0B00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA07123-52EA-314A-81EF-989A42CB4DFE}">
+  <dimension ref="A2:F22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="6" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D036245-91C1-5842-93DD-735018175DE8}">
+  <dimension ref="B2:R24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="7" max="7" width="4" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" customWidth="1"/>
+    <col min="13" max="13" width="3" customWidth="1"/>
+    <col min="16" max="16" width="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B2" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="E2" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="58"/>
+      <c r="H2" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" s="58"/>
+      <c r="K2" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="L2" s="58"/>
+      <c r="N2" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="O2" s="58"/>
+      <c r="Q2" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="R2" s="58"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="E3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="38"/>
+      <c r="H3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="38"/>
+      <c r="K3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="38"/>
+      <c r="N3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" s="38"/>
+      <c r="Q3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="R3" s="38"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C3C734-6227-7445-884D-1F1A5F3909C7}">
+  <dimension ref="B2:R24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="7" max="7" width="4" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" customWidth="1"/>
+    <col min="13" max="13" width="3" customWidth="1"/>
+    <col min="16" max="16" width="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B2" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="63"/>
+      <c r="E2" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="59"/>
+      <c r="H2" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="I2" s="59"/>
+      <c r="K2" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="L2" s="59"/>
+      <c r="N2" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="O2" s="59"/>
+      <c r="Q2" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="R2" s="59"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="E3" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="40"/>
+      <c r="H3" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="40"/>
+      <c r="K3" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="40"/>
+      <c r="N3" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" s="40"/>
+      <c r="Q3" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="R3" s="40"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="N2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB4949D-EAAF-AE4C-9BAF-D5BF753E34CD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A900FC-A692-B445-95C9-59E70352B291}">
+  <dimension ref="A2:AG51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
+    <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
+    <col min="11" max="31" width="8.5" customWidth="1"/>
+    <col min="32" max="32" width="8.5" style="1" customWidth="1"/>
+    <col min="33" max="33" width="8.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="K2" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="U2" s="6"/>
+      <c r="AA2" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="K3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+      <c r="U3" s="14"/>
+      <c r="AA3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>60</v>
+      </c>
+      <c r="U4" s="14"/>
+      <c r="AA4" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" t="s">
+        <v>207</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="U5" s="14"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="9"/>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="K6" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C8" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="51"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="1"/>
+      <c r="R8" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="S8" s="50"/>
+      <c r="T8" s="50"/>
+      <c r="U8" s="50"/>
+      <c r="V8" s="50"/>
+      <c r="W8" s="50"/>
+      <c r="X8" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y8" s="50"/>
+      <c r="Z8" s="50"/>
+      <c r="AA8" s="50"/>
+      <c r="AB8" s="50"/>
+      <c r="AC8" s="50"/>
+      <c r="AD8" s="50"/>
+      <c r="AE8" s="50"/>
+      <c r="AF8" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG8" s="50"/>
+    </row>
+    <row r="9" spans="1:33" ht="18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="P9" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q9" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="R9" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="S9" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="T9" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="U9" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="V9" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="X9" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y9" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z9" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA9" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB9" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC9" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD9" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="AE9" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="AF9" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG9" s="30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>soil</t>
+        </is>
+      </c>
+      <c r="C10" s="3">
+        <v>120.0</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>mc</t>
+        </is>
+      </c>
+      <c r="F10" s="3">
+        <v>200.0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="U10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>lf</t>
+        </is>
+      </c>
+      <c r="AB10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>2000000.0</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -12624,10 +13492,19 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="18"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -12652,10 +13529,19 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="18"/>
+      <c r="AE12" s="19"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -12680,10 +13566,19 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -12708,10 +13603,19 @@
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -12736,10 +13640,19 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -12764,10 +13677,19 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -12792,10 +13714,19 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="3"/>
+      <c r="AG17" s="3"/>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -12820,10 +13751,19 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -12848,10 +13788,19 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -12876,10 +13825,19 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -12904,10 +13862,19 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -12932,10 +13899,19 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -12960,24 +13936,54 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J25" s="1"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>15</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -12985,9 +13991,22 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J26" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -12995,9 +14014,14 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J27" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -13005,9 +14029,14 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J28" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -13015,9 +14044,14 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J29" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -13025,9 +14059,14 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J30" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -13035,9 +14074,14 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J31" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -13045,9 +14089,14 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J32" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -13055,9 +14104,14 @@
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
-    </row>
-    <row r="33" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J33" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+    </row>
+    <row r="33" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -13065,9 +14119,14 @@
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
-    </row>
-    <row r="34" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J34" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+    </row>
+    <row r="34" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -13075,9 +14134,14 @@
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
-    </row>
-    <row r="35" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J35" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+    </row>
+    <row r="35" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -13085,9 +14149,14 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-    </row>
-    <row r="36" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J36" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+    </row>
+    <row r="36" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -13095,9 +14164,14 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
-    </row>
-    <row r="37" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J37" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+    </row>
+    <row r="37" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -13105,9 +14179,14 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-    </row>
-    <row r="38" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J38" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+    </row>
+    <row r="38" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -13115,9 +14194,14 @@
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
-    </row>
-    <row r="39" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J39" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -13125,9 +14209,14 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
-    </row>
-    <row r="40" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J40" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+    </row>
+    <row r="40" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -13135,9 +14224,14 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-    </row>
-    <row r="41" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J41" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+    </row>
+    <row r="41" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -13145,9 +14239,14 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
-    </row>
-    <row r="42" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J42" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+    </row>
+    <row r="42" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -13155,9 +14254,14 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
-    </row>
-    <row r="43" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J43" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+    </row>
+    <row r="43" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -13165,9 +14269,14 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
-    </row>
-    <row r="44" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J44" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+    </row>
+    <row r="44" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -13175,9 +14284,14 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
-    </row>
-    <row r="45" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J45" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+    </row>
+    <row r="45" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -13185,9 +14299,14 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
-    </row>
-    <row r="46" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J46" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+    </row>
+    <row r="46" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -13195,9 +14314,14 @@
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
-    </row>
-    <row r="47" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J47" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+    </row>
+    <row r="47" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -13205,9 +14329,14 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-    </row>
-    <row r="48" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J48" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+    </row>
+    <row r="48" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -13215,9 +14344,14 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
-    </row>
-    <row r="49" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J49" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+    </row>
+    <row r="49" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -13225,9 +14359,14 @@
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
-    </row>
-    <row r="50" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J50" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
+    </row>
+    <row r="50" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -13235,50 +14374,104 @@
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+    </row>
+    <row r="51" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="L7:Q7"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="R7:V7"/>
+    <mergeCell ref="C8:O8"/>
+    <mergeCell ref="R8:W8"/>
+    <mergeCell ref="AF8:AG8"/>
+    <mergeCell ref="X8:AE8"/>
   </mergeCells>
-  <conditionalFormatting sqref="F9:F50">
-    <cfRule type="expression" dxfId="8" priority="1">
-      <formula>$D9="cp"</formula>
+  <conditionalFormatting sqref="F10:I51">
+    <cfRule type="expression" dxfId="14" priority="16">
+      <formula>$E10="pow"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9:H50">
-    <cfRule type="expression" dxfId="7" priority="2">
-      <formula>$D9="mc"</formula>
+  <conditionalFormatting sqref="G10:G51">
+    <cfRule type="expression" dxfId="13" priority="5">
+      <formula>$E10="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:J50">
-    <cfRule type="expression" dxfId="6" priority="3">
-      <formula>$D9="cp"</formula>
+  <conditionalFormatting sqref="H10:I51">
+    <cfRule type="expression" dxfId="12" priority="4">
+      <formula>$E10="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N9:N50">
-    <cfRule type="expression" dxfId="5" priority="4">
-      <formula>$D9="cp"</formula>
+  <conditionalFormatting sqref="J10:K51">
+    <cfRule type="expression" dxfId="11" priority="6">
+      <formula>$E10="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O9:O50">
-    <cfRule type="expression" dxfId="4" priority="6">
-      <formula>$D9="mc"</formula>
+  <conditionalFormatting sqref="L10:O51">
+    <cfRule type="expression" dxfId="10" priority="19">
+      <formula>AND($E10&lt;&gt;"",$E10&lt;&gt;"pow")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P9:Q50">
-    <cfRule type="expression" dxfId="3" priority="5">
-      <formula>$D9="cp"</formula>
+  <conditionalFormatting sqref="Q10:Q51">
+    <cfRule type="expression" dxfId="9" priority="20">
+      <formula>AND($P10&lt;&gt;"",$P10&lt;&gt;"ru")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9:D50" xr:uid="{374AFD2C-B540-DD4B-A245-8B781F76E64C}">
-      <formula1>$C$3:$C$4</formula1>
+  <conditionalFormatting sqref="S10:U51">
+    <cfRule type="expression" dxfId="8" priority="21">
+      <formula>$E10="pow"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T10:T51">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$E10="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U10:U51">
+    <cfRule type="expression" dxfId="6" priority="15">
+      <formula>$E10="mc"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V10:W51">
+    <cfRule type="expression" dxfId="5" priority="10">
+      <formula>$E10="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB10:AC101">
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>$AA10="vg"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD10:AE101">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$AA10="lf"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E51" xr:uid="{374AFD2C-B540-DD4B-A245-8B781F76E64C}">
+      <formula1>$C$3:$C$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K9:K50" xr:uid="{D770415C-1ECE-F44B-9D8C-08EF1CF31C8E}">
-      <formula1>$J$3:$J$5</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P10:P51" xr:uid="{D770415C-1ECE-F44B-9D8C-08EF1CF31C8E}">
+      <formula1>$K$3:$K$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA10:AA101" xr:uid="{E00A94A9-D864-5843-8FBD-E84775B1C100}">
+      <formula1>$AA$3:$AA$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13286,7 +14479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4436F470-A09D-8C49-9B48-FB04FA2826AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D14E9FA-AFF6-A74D-8120-64FF6A371536}">
   <dimension ref="A2:AR27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -13316,266 +14509,268 @@
         <v>46</v>
       </c>
       <c r="B2" s="3">
-        <v>-10</v>
+        <v>-10.0</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="A4" s="53" t="inlineStr">
+        <is>
+          <t>Profile Line #1</t>
+        </is>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="D4" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="G4" s="52" t="s">
+      <c r="E4" s="53"/>
+      <c r="G4" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="J4" s="52" t="s">
+      <c r="H4" s="53"/>
+      <c r="J4" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="52"/>
-      <c r="M4" s="52" t="s">
+      <c r="K4" s="53"/>
+      <c r="M4" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="52"/>
-      <c r="P4" s="52" t="s">
+      <c r="N4" s="53"/>
+      <c r="P4" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="52"/>
+      <c r="Q4" s="53"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="52" t="s">
+      <c r="S4" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="52"/>
+      <c r="T4" s="53"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="52" t="s">
+      <c r="V4" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="52"/>
+      <c r="W4" s="53"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="52" t="s">
+      <c r="Y4" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="52"/>
+      <c r="Z4" s="53"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="52" t="s">
+      <c r="AB4" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="52"/>
-      <c r="AE4" s="52" t="s">
+      <c r="AC4" s="53"/>
+      <c r="AE4" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF4" s="53"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI4" s="53"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL4" s="53"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="AF4" s="52"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="52" t="s">
+      <c r="AO4" s="53"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="AL4" s="52"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="AO4" s="52"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="AR4" s="52"/>
+      <c r="AR4" s="53"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B5" s="42">
         <v>1</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E5" s="42">
         <v>2</v>
       </c>
       <c r="G5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H5" s="42">
         <v>3</v>
       </c>
       <c r="J5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K5" s="42">
         <v>4</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N5" s="42">
         <v>5</v>
       </c>
       <c r="P5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q5" s="42">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="T5" s="42">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="W5" s="42">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Z5" s="42">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AC5" s="42">
         <v>10</v>
       </c>
       <c r="AE5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AF5" s="42">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AI5" s="42">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AL5" s="42">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AO5" s="42">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AR5" s="42">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="50" t="str">
+      <c r="A6" s="54" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v>soil</v>
-      </c>
-      <c r="B6" s="51"/>
-      <c r="D6" s="50" t="str">
+        <v/>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="D6" s="54" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="51"/>
-      <c r="G6" s="50" t="str">
+      <c r="E6" s="55"/>
+      <c r="G6" s="54" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="51"/>
-      <c r="J6" s="50" t="str">
+      <c r="H6" s="55"/>
+      <c r="J6" s="54" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="51"/>
-      <c r="M6" s="50" t="str">
+      <c r="K6" s="55"/>
+      <c r="M6" s="54" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="51"/>
-      <c r="P6" s="50" t="str">
+      <c r="N6" s="55"/>
+      <c r="P6" s="54" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="51"/>
+      <c r="Q6" s="55"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="50" t="str">
+      <c r="S6" s="54" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="51"/>
+      <c r="T6" s="55"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="50" t="str">
+      <c r="V6" s="54" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="51"/>
+      <c r="W6" s="55"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="50" t="str">
+      <c r="Y6" s="54" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="51"/>
+      <c r="Z6" s="55"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="50" t="str">
+      <c r="AB6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="51"/>
-      <c r="AE6" s="50" t="str">
+      <c r="AC6" s="55"/>
+      <c r="AE6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="51"/>
+      <c r="AF6" s="55"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="50" t="str">
+      <c r="AH6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="51"/>
+      <c r="AI6" s="55"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="50" t="str">
+      <c r="AK6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="51"/>
+      <c r="AL6" s="55"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="50" t="str">
+      <c r="AN6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="51"/>
+      <c r="AO6" s="55"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="50" t="str">
+      <c r="AQ6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="51"/>
+      <c r="AR6" s="55"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -13679,10 +14874,10 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>-30</v>
+        <v>-30.0</v>
       </c>
       <c r="B8" s="3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -13723,10 +14918,10 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -13767,10 +14962,10 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="B10" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -13811,10 +15006,10 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>80</v>
+        <v>80.0</v>
       </c>
       <c r="B11" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -14495,43 +15690,43 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D531F6A4-7395-D742-B12A-DB33E9D92D43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88992C43-9D03-6445-8931-028E950C2356}">
   <dimension ref="A2:AR27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -14558,263 +15753,263 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="D4" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="53"/>
+      <c r="G4" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" s="53"/>
+      <c r="J4" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="K4" s="53"/>
+      <c r="M4" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="G4" s="52" t="s">
+      <c r="N4" s="53"/>
+      <c r="P4" s="53" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="J4" s="52" t="s">
+      <c r="Q4" s="53"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="53" t="s">
         <v>156</v>
       </c>
-      <c r="K4" s="52"/>
-      <c r="M4" s="52" t="s">
+      <c r="T4" s="53"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="52"/>
-      <c r="P4" s="52" t="s">
+      <c r="W4" s="53"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="53" t="s">
         <v>158</v>
       </c>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="52" t="s">
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="T4" s="52"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="52" t="s">
+      <c r="AC4" s="53"/>
+      <c r="AE4" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="W4" s="52"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="52" t="s">
+      <c r="AF4" s="53"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="52" t="s">
+      <c r="AI4" s="53"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="AC4" s="52"/>
-      <c r="AE4" s="52" t="s">
+      <c r="AL4" s="53"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="AF4" s="52"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="52" t="s">
+      <c r="AO4" s="53"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="AL4" s="52"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="52" t="s">
-        <v>166</v>
-      </c>
-      <c r="AO4" s="52"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="AR4" s="52"/>
+      <c r="AR4" s="53"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B5" s="44">
         <v>1</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E5" s="44">
         <v>2</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H5" s="44">
         <v>3</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K5" s="44">
         <v>4</v>
       </c>
       <c r="M5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N5" s="44">
         <v>5</v>
       </c>
       <c r="P5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q5" s="44">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="T5" s="44">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="W5" s="44">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Z5" s="44">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AC5" s="44">
         <v>10</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AF5" s="44">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AI5" s="44">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AL5" s="44">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AO5" s="44">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AR5" s="44">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="str">
+      <c r="A6" s="56" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v>soil</v>
-      </c>
-      <c r="B6" s="54"/>
-      <c r="D6" s="53" t="str">
+        <v/>
+      </c>
+      <c r="B6" s="57"/>
+      <c r="D6" s="56" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="54"/>
-      <c r="G6" s="53" t="str">
+      <c r="E6" s="57"/>
+      <c r="G6" s="56" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="54"/>
-      <c r="J6" s="53" t="str">
+      <c r="H6" s="57"/>
+      <c r="J6" s="56" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="54"/>
-      <c r="M6" s="53" t="str">
+      <c r="K6" s="57"/>
+      <c r="M6" s="56" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="54"/>
-      <c r="P6" s="53" t="str">
+      <c r="N6" s="57"/>
+      <c r="P6" s="56" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="54"/>
+      <c r="Q6" s="57"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="53" t="str">
+      <c r="S6" s="56" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="54"/>
+      <c r="T6" s="57"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="53" t="str">
+      <c r="V6" s="56" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="54"/>
+      <c r="W6" s="57"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="53" t="str">
+      <c r="Y6" s="56" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="54"/>
+      <c r="Z6" s="57"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="53" t="str">
+      <c r="AB6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="54"/>
-      <c r="AE6" s="53" t="str">
+      <c r="AC6" s="57"/>
+      <c r="AE6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="54"/>
+      <c r="AF6" s="57"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="53" t="str">
+      <c r="AH6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="54"/>
+      <c r="AI6" s="57"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="53" t="str">
+      <c r="AK6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="54"/>
+      <c r="AL6" s="57"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="53" t="str">
+      <c r="AN6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="54"/>
+      <c r="AO6" s="57"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="53" t="str">
+      <c r="AQ6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="54"/>
+      <c r="AR6" s="57"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -15718,12 +16913,14 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AQ4:AR4"/>
@@ -15740,21 +16937,19 @@
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3821B4BC-2D03-B047-9DB8-8ECD257276B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E1F343-68A5-3340-AF23-43D8E7E1F914}">
   <dimension ref="A2:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -15763,14 +16958,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="D2" s="56" t="s">
+      <c r="B2" s="58"/>
+      <c r="D2" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="56"/>
+      <c r="E2" s="59"/>
       <c r="G2" s="24" t="s">
         <v>83</v>
       </c>
@@ -15919,7 +17114,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE6F868-4227-8740-A8A1-4745562882FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E0556E9-786A-E84F-BF20-677A5EE9D63D}">
   <dimension ref="A2:N16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -15965,16 +17160,18 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C3" s="3">
-        <v>40</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>40.0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
       </c>
       <c r="E3" s="3">
-        <v>-10</v>
+        <v>-10.0</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -16114,17 +17311,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E42">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G42">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>OR($D3="Depth",$D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H42">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>OR($D3="Depth",$D3="Intercept")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16138,7 +17335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B481A4B-5762-2B4B-BD1E-7996162F3A9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620242D-B699-0640-AD9C-590D8F82AC0F}">
   <dimension ref="A2:F23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -16298,7 +17495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7976BB56-7732-404C-B58A-55DA7F8052B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D19B78E-FBCC-4E41-BB37-C8D0D27B23E8}">
   <dimension ref="B2:X22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -16317,36 +17514,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="60" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="F2" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="J2" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="N2" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="F2" s="57" t="s">
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="R2" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="J2" s="57" t="s">
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="V2" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="N2" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="R2" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="V2" s="57" t="s">
-        <v>132</v>
-      </c>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="318">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -992,6 +992,167 @@
   </si>
   <si>
     <t>auto</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c/p)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(d)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>sat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>q</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3243,7 +3404,7 @@
         <v>270</v>
       </c>
       <c r="H2" s="40" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="I2" s="40" t="s">
         <v>253</v>
@@ -5774,7 +5935,7 @@
         <v>111</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>112</v>
+        <v>316</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>113</v>
@@ -5843,22 +6004,22 @@
         <v>133</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>134</v>
+        <v>311</v>
       </c>
       <c r="AB10" s="46" t="s">
-        <v>135</v>
+        <v>312</v>
       </c>
       <c r="AC10" s="47" t="s">
         <v>136</v>
       </c>
       <c r="AD10" s="46" t="s">
-        <v>137</v>
+        <v>313</v>
       </c>
       <c r="AE10" s="46" t="s">
-        <v>138</v>
+        <v>314</v>
       </c>
       <c r="AF10" s="47" t="s">
-        <v>139</v>
+        <v>315</v>
       </c>
       <c r="AG10" s="23" t="s">
         <v>140</v>

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>pile</t>
+          <t>lower row</t>
         </is>
       </c>
       <c r="C3" s="3">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>pile</t>
+          <t>upper row</t>
         </is>
       </c>
       <c r="C4" s="3">

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11708D50-B4AE-4447-916E-877A7873BC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC02AEA9-EA56-1649-9CD0-1ADB754CC06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33220" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18260" yWindow="3440" windowWidth="44060" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="311">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -223,6 +223,12 @@
     <t>Water loads:</t>
   </si>
   <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>Surface family:</t>
+  </si>
+  <si>
     <t>Unit Options:</t>
   </si>
   <si>
@@ -397,9 +403,6 @@
     <t>g</t>
   </si>
   <si>
-    <t>gsat</t>
-  </si>
-  <si>
     <t>option</t>
   </si>
   <si>
@@ -463,24 +466,9 @@
     <t>hb_d</t>
   </si>
   <si>
-    <t>s(g)</t>
-  </si>
-  <si>
-    <t>s(c)</t>
-  </si>
-  <si>
     <t>s(f)</t>
   </si>
   <si>
-    <t>s(c/p)</t>
-  </si>
-  <si>
-    <t>s(d)</t>
-  </si>
-  <si>
-    <t>s(psi)</t>
-  </si>
-  <si>
     <t>k1</t>
   </si>
   <si>
@@ -874,9 +862,6 @@
     <t>H</t>
   </si>
   <si>
-    <t>qp</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -991,7 +976,24 @@
     <t>save_times</t>
   </si>
   <si>
-    <t>auto</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1048,26 +1050,6 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(c)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Symbol"/>
-        <charset val="2"/>
-      </rPr>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>(c/p)</t>
     </r>
   </si>
@@ -1130,28 +1112,6 @@
         <rFont val="Aptos Narrow"/>
       </rPr>
       <t>sat</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Symbol"/>
-        <charset val="2"/>
-      </rPr>
-      <t>q</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>p</t>
     </r>
   </si>
 </sst>
@@ -1614,16 +1574,16 @@
     <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1917,6 +1877,570 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>217714</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>54430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>199571</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9071</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B0FB8E9-E4E3-974A-BE46-8E599C58A56D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14804571" y="254001"/>
+          <a:ext cx="3610429" cy="3746499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Label</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = name used in error messages, summaries, and plots</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>(x1, y1), (x2, y2) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= start and end of reinforcement line</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Type</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = support preset, fills Dir and Appl: Geosynthetic (Tangent, Active), Nail (Axial, Passive), Tieback (Axial, Active), Anchor (Axial, Active)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Dir</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force direction at the slip surface (LEM only): Tangent = reorients along slip surface (flexible); Axial = along the reinforcement line (rigid). Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS. Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tmax</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = tensile capacity (force/length; or force per element if Spacing is given)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Lp1, Lp2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= pullout length at end 1 / end 2 (0 = fully anchored)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tend1, Tend2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= anchorage/plate/connection capacity at end 1 / end 2 (0 = friction only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Spacing</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = out-of-plane spacing for discrete supports (nails, tiebacks); blank or 1 for geosynthetics</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tres</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = residual capacity after rupture (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = modulus of elasticity of reinforcement (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Area</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>308429</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>571501</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>145143</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6B716B0-439A-6440-8742-7BC140EF924C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13398500" y="190499"/>
+          <a:ext cx="3156858" cy="2349501"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>(x1,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t> y1), (x2, y2) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>= top and bottom of pile</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>H</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = Pile force magnitude (kN/m or lb/ft). </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>D</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Pile diameter</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (ft or m)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t> = center to center pile spacing</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> (ft or m)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Vcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Shear</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> capacity of pile (force)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Mcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Moment capacity of pile (force x length)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = Young's modulus of pile material (force/lengh^2)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>I </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>= </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Moment of inertia (length^4)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Area</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Cross-sectional area (length^2)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Fixity</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile head status (fixed or free)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2261,15 +2785,15 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
       <c r="F7" s="15" t="s">
         <v>4</v>
       </c>
@@ -2479,15 +3003,19 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D50" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="4:4" x14ac:dyDescent="0.2">
@@ -2497,22 +3025,22 @@
     </row>
     <row r="53" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D53" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D54" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D56" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="4:4" x14ac:dyDescent="0.2">
@@ -2522,7 +3050,7 @@
     </row>
     <row r="59" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D59" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
@@ -2532,89 +3060,89 @@
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D61" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D63" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D64" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D65" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D66" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D68" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D69" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D70" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D71" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D73" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D74" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D75" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D76" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D77" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D78" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B7:D7"/>
   </mergeCells>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
@@ -2636,6 +3164,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+      <formula1>"circular,non-circular"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2656,67 +3187,67 @@
   <sheetData>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="H2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="I2" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="J2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="K2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="L2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="M2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="N2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="O2" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="P2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="Q2" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="R2" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="Z2" t="s">
         <v>258</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="AA2" t="s">
         <v>259</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="AB2" t="s">
         <v>260</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="R2" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>262</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>263</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -2747,13 +3278,13 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="Z3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AA3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AB3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -2784,7 +3315,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="Z4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -2815,7 +3346,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="Z5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -2902,13 +3433,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="Z8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AA8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AB8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -2939,13 +3470,13 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="Z9" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AA9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AB9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -2976,13 +3507,13 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="Z10" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AA10" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AB10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
@@ -3013,13 +3544,13 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="Z11" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AA11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AB11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -3333,7 +3864,7 @@
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="T23" s="42"/>
       <c r="U23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
@@ -3341,7 +3872,7 @@
       <c r="L24" s="9"/>
       <c r="T24" s="26"/>
       <c r="U24" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
@@ -3349,7 +3880,7 @@
       <c r="L25" s="9"/>
       <c r="T25" s="29"/>
       <c r="U25" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3365,82 +3896,80 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:AA18"/>
+  <dimension ref="A2:Z17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
-    <col min="3" max="8" width="10.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="17" width="10.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5" customWidth="1"/>
+    <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="16" width="10.83203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="H2" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="G2" s="40" t="s">
+      <c r="I2" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="K2" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="L2" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="H2" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="J2" s="27" t="s">
+      <c r="M2" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="P2" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="K2" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="L2" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="M2" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="O2" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="P2" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>277</v>
+      <c r="Y2" t="s">
+        <v>222</v>
       </c>
       <c r="Z2" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3463,37 +3992,36 @@
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3">
+        <v>2.0</v>
+      </c>
       <c r="J3" s="3">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="K3" s="3">
-        <v>6.0</v>
+        <v>46000.0</v>
       </c>
       <c r="L3" s="3">
-        <v>46000.0</v>
+        <v>60000.0</v>
       </c>
       <c r="M3" s="3">
-        <v>60000.0</v>
-      </c>
-      <c r="N3" s="3">
         <v>518400000.0</v>
       </c>
+      <c r="N3" s="3"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>free</t>
         </is>
       </c>
+      <c r="Y3" t="s">
+        <v>226</v>
+      </c>
       <c r="Z3" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3516,31 +4044,30 @@
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="I4" s="3">
+        <v>2.0</v>
+      </c>
       <c r="J4" s="3">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="K4" s="3">
-        <v>6.0</v>
+        <v>46000.0</v>
       </c>
       <c r="L4" s="3">
-        <v>46000.0</v>
+        <v>60000.0</v>
       </c>
       <c r="M4" s="3">
-        <v>60000.0</v>
-      </c>
-      <c r="N4" s="3">
         <v>518400000.0</v>
       </c>
+      <c r="N4" s="3"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>free</t>
         </is>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -3559,9 +4086,8 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -3580,9 +4106,8 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -3601,9 +4126,8 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -3622,9 +4146,8 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -3643,9 +4166,8 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -3664,9 +4186,8 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3685,9 +4206,8 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3706,44 +4226,40 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="I14" s="9"/>
       <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="S16" s="42"/>
-      <c r="T16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S17" s="26"/>
-      <c r="T17" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S18" s="29"/>
-      <c r="T18" s="9" t="s">
-        <v>102</v>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="R15" s="42"/>
+      <c r="S15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="R16" s="26"/>
+      <c r="S16" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="18:19" x14ac:dyDescent="0.2">
+      <c r="R17" s="29"/>
+      <c r="S17" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Y$2:$Y$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
       <formula1>$Z$2:$Z$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3759,22 +4275,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -3997,99 +4513,99 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>281</v>
-      </c>
-      <c r="F2" s="54"/>
+        <v>276</v>
+      </c>
+      <c r="F2" s="52"/>
       <c r="H2" s="59" t="s">
-        <v>282</v>
-      </c>
-      <c r="I2" s="54"/>
+        <v>277</v>
+      </c>
+      <c r="I2" s="52"/>
       <c r="K2" s="59" t="s">
-        <v>283</v>
-      </c>
-      <c r="L2" s="54"/>
+        <v>278</v>
+      </c>
+      <c r="L2" s="52"/>
       <c r="N2" s="59" t="s">
-        <v>284</v>
-      </c>
-      <c r="O2" s="54"/>
+        <v>279</v>
+      </c>
+      <c r="O2" s="52"/>
       <c r="Q2" s="59" t="s">
-        <v>285</v>
-      </c>
-      <c r="R2" s="54"/>
+        <v>280</v>
+      </c>
+      <c r="R2" s="52"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F3" s="33"/>
       <c r="H3" s="32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I3" s="33"/>
       <c r="K3" s="32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="R4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="U4" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4106,10 +4622,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="U5" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4126,7 +4642,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4415,99 +4931,99 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>293</v>
-      </c>
-      <c r="F2" s="54"/>
+        <v>288</v>
+      </c>
+      <c r="F2" s="52"/>
       <c r="H2" s="60" t="s">
-        <v>294</v>
-      </c>
-      <c r="I2" s="54"/>
+        <v>289</v>
+      </c>
+      <c r="I2" s="52"/>
       <c r="K2" s="60" t="s">
-        <v>295</v>
-      </c>
-      <c r="L2" s="54"/>
+        <v>290</v>
+      </c>
+      <c r="L2" s="52"/>
       <c r="N2" s="60" t="s">
-        <v>296</v>
-      </c>
-      <c r="O2" s="54"/>
+        <v>291</v>
+      </c>
+      <c r="O2" s="52"/>
       <c r="Q2" s="60" t="s">
-        <v>297</v>
-      </c>
-      <c r="R2" s="54"/>
+        <v>292</v>
+      </c>
+      <c r="R2" s="52"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="R4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="U4" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4524,10 +5040,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="U5" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4826,22 +5342,22 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>297</v>
+      </c>
+      <c r="G2" s="50" t="s">
         <v>298</v>
-      </c>
-      <c r="C2" s="50" t="s">
-        <v>299</v>
-      </c>
-      <c r="D2" s="50" t="s">
-        <v>300</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>301</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -4852,7 +5368,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -4874,7 +5390,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -4896,7 +5412,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -4908,7 +5424,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -4920,7 +5436,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -4940,7 +5456,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="J11" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -5762,294 +6278,294 @@
   <sheetData>
     <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AD2" s="6"/>
       <c r="AJ2" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AD3" s="14"/>
       <c r="AJ3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AK3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L4" s="42"/>
       <c r="M4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="P4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AD4" s="14"/>
       <c r="AJ4" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AK4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AJ5" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK5" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C9" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="54"/>
-      <c r="X9" s="54"/>
-      <c r="Y9" s="54"/>
-      <c r="Z9" s="54"/>
-      <c r="AA9" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB9" s="54"/>
-      <c r="AC9" s="54"/>
-      <c r="AD9" s="54"/>
-      <c r="AE9" s="54"/>
-      <c r="AF9" s="54"/>
-      <c r="AG9" s="53" t="s">
+      <c r="C9" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="AH9" s="54"/>
-      <c r="AI9" s="54"/>
-      <c r="AJ9" s="54"/>
-      <c r="AK9" s="54"/>
-      <c r="AL9" s="54"/>
-      <c r="AM9" s="54"/>
-      <c r="AN9" s="54"/>
-      <c r="AO9" s="54"/>
-      <c r="AP9" s="54"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52"/>
+      <c r="Q9" s="52"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="52"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="52"/>
+      <c r="V9" s="52"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="52"/>
+      <c r="Z9" s="52"/>
+      <c r="AA9" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB9" s="52"/>
+      <c r="AC9" s="52"/>
+      <c r="AD9" s="52"/>
+      <c r="AE9" s="52"/>
+      <c r="AF9" s="52"/>
+      <c r="AG9" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="52"/>
+      <c r="AK9" s="52"/>
+      <c r="AL9" s="52"/>
+      <c r="AM9" s="52"/>
+      <c r="AN9" s="52"/>
+      <c r="AO9" s="52"/>
+      <c r="AP9" s="52"/>
     </row>
     <row r="10" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G10" s="45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K10" s="49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M10" s="21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N10" s="43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O10" s="44" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P10" s="44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q10" s="44" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R10" s="44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S10" s="44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T10" s="44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U10" s="44" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="V10" s="44" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="W10" s="44" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="X10" s="44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Y10" s="44" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Z10" s="44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AB10" s="46" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="AC10" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD10" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="AE10" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="AF10" s="47" t="s">
+        <v>309</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AD10" s="46" t="s">
-        <v>313</v>
-      </c>
-      <c r="AE10" s="46" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>315</v>
-      </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="AI10" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ10" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AP10" s="23" t="s">
         <v>145</v>
-      </c>
-      <c r="AM10" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="AN10" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="AO10" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="AP10" s="23" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.2">
@@ -7608,16 +8124,16 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B2" s="3">
         <v>-10.0</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N2" s="24" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -7626,167 +8142,167 @@
           <t>Profile Line #1</t>
         </is>
       </c>
-      <c r="B4" s="52"/>
+      <c r="B4" s="53"/>
       <c r="D4" s="55" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="53"/>
+      <c r="G4" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" s="53"/>
+      <c r="J4" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="K4" s="53"/>
+      <c r="M4" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="N4" s="53"/>
+      <c r="P4" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="G4" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" s="52"/>
-      <c r="J4" s="55" t="s">
-        <v>156</v>
-      </c>
-      <c r="K4" s="52"/>
-      <c r="M4" s="55" t="s">
-        <v>157</v>
-      </c>
-      <c r="N4" s="52"/>
-      <c r="P4" s="55" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q4" s="54"/>
+      <c r="Q4" s="52"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>159</v>
-      </c>
-      <c r="T4" s="54"/>
+        <v>155</v>
+      </c>
+      <c r="T4" s="52"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="W4" s="54"/>
+        <v>156</v>
+      </c>
+      <c r="W4" s="52"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>161</v>
-      </c>
-      <c r="Z4" s="54"/>
+        <v>157</v>
+      </c>
+      <c r="Z4" s="52"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>162</v>
-      </c>
-      <c r="AC4" s="54"/>
+        <v>158</v>
+      </c>
+      <c r="AC4" s="52"/>
       <c r="AE4" s="55" t="s">
-        <v>163</v>
-      </c>
-      <c r="AF4" s="54"/>
+        <v>159</v>
+      </c>
+      <c r="AF4" s="52"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI4" s="54"/>
+        <v>160</v>
+      </c>
+      <c r="AI4" s="52"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>165</v>
-      </c>
-      <c r="AL4" s="54"/>
+        <v>161</v>
+      </c>
+      <c r="AL4" s="52"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>166</v>
-      </c>
-      <c r="AO4" s="54"/>
+        <v>162</v>
+      </c>
+      <c r="AO4" s="52"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>167</v>
-      </c>
-      <c r="AR4" s="54"/>
+        <v>163</v>
+      </c>
+      <c r="AR4" s="52"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -7879,172 +8395,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AR8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -8865,6 +9381,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -8874,27 +9404,13 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8928,277 +9444,277 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="D4" s="55" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="53"/>
+      <c r="G4" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="53"/>
+      <c r="J4" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="K4" s="53"/>
+      <c r="M4" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="D4" s="55" t="s">
+      <c r="N4" s="53"/>
+      <c r="P4" s="55" t="s">
         <v>175</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="G4" s="55" t="s">
-        <v>176</v>
-      </c>
-      <c r="H4" s="52"/>
-      <c r="J4" s="55" t="s">
-        <v>177</v>
-      </c>
-      <c r="K4" s="52"/>
-      <c r="M4" s="55" t="s">
-        <v>178</v>
-      </c>
-      <c r="N4" s="52"/>
-      <c r="P4" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q4" s="54"/>
+      <c r="Q4" s="52"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>180</v>
-      </c>
-      <c r="T4" s="54"/>
+        <v>176</v>
+      </c>
+      <c r="T4" s="52"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="W4" s="54"/>
+        <v>177</v>
+      </c>
+      <c r="W4" s="52"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z4" s="54"/>
+        <v>178</v>
+      </c>
+      <c r="Z4" s="52"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="AC4" s="54"/>
+        <v>179</v>
+      </c>
+      <c r="AC4" s="52"/>
       <c r="AE4" s="55" t="s">
-        <v>184</v>
-      </c>
-      <c r="AF4" s="54"/>
+        <v>180</v>
+      </c>
+      <c r="AF4" s="52"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>185</v>
-      </c>
-      <c r="AI4" s="54"/>
+        <v>181</v>
+      </c>
+      <c r="AI4" s="52"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL4" s="54"/>
+        <v>182</v>
+      </c>
+      <c r="AL4" s="52"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>187</v>
-      </c>
-      <c r="AO4" s="54"/>
+        <v>183</v>
+      </c>
+      <c r="AO4" s="52"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="AR4" s="54"/>
+        <v>184</v>
+      </c>
+      <c r="AR4" s="52"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Q5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="T5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="W5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Z5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AC5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AE5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AF5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AI5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AL5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AO5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AR5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K6" s="39">
         <v>4</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N6" s="39">
         <v>5</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Q6" s="39">
         <v>6</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T6" s="39">
         <v>7</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="W6" s="39">
         <v>8</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -9291,172 +9807,172 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B8" s="39"/>
       <c r="D8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N8" s="39"/>
       <c r="P8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="W8" s="39"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AO9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AR9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -10261,35 +10777,35 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AN7:AO7"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AQ7:AR7"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="S7:T7"/>
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="Y7:Z7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="AQ7:AR7"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="Y7:Z7"/>
+    <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="Y4:Z4"/>
     <mergeCell ref="AE7:AF7"/>
     <mergeCell ref="AK7:AL7"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="AN7:AO7"/>
     <mergeCell ref="AH7:AI7"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
@@ -10387,20 +10903,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>191</v>
-      </c>
-      <c r="B2" s="54"/>
+        <v>187</v>
+      </c>
+      <c r="B2" s="52"/>
       <c r="D2" s="60" t="s">
-        <v>192</v>
-      </c>
-      <c r="E2" s="54"/>
+        <v>188</v>
+      </c>
+      <c r="E2" s="52"/>
       <c r="G2" s="22" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -10408,7 +10924,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -10419,19 +10935,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -10444,7 +10960,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -10453,10 +10969,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -10593,31 +11109,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -10645,10 +11161,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -10663,10 +11179,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -10681,10 +11197,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K5" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -10711,7 +11227,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -10726,7 +11242,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="K8"/>
     </row>
@@ -10742,7 +11258,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K9"/>
     </row>
@@ -10758,7 +11274,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="K10"/>
     </row>
@@ -10774,7 +11290,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K11"/>
     </row>
@@ -10790,31 +11306,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -10823,7 +11339,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="K17"/>
     </row>
@@ -10864,16 +11380,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -10884,10 +11400,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -10895,10 +11411,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -10906,10 +11422,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11039,122 +11555,122 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -11539,18 +12055,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="V5:W5"/>
+    <mergeCell ref="F4:H4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:O5"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5 H5 L5 P5 T5 X5" xr:uid="{00000000-0002-0000-0700-000000000000}">
@@ -11588,122 +12104,122 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12088,18 +12604,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="V5:W5"/>
+    <mergeCell ref="F4:H4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:O5"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5 H5 L5 P5 T5 X5" xr:uid="{00000000-0002-0000-0800-000000000000}">

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -3991,7 +3991,11 @@
         <v>-10.0</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="I3" s="3">
         <v>2.0</v>
       </c>
@@ -4043,7 +4047,11 @@
         <v>-10.0</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="I4" s="3">
         <v>2.0</v>
       </c>

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -6612,7 +6612,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
       <c r="M11" s="3">
         <v>2000000.0</v>
       </c>

--- a/docs/lem/files/xslope_piles.xlsx
+++ b/docs/lem/files/xslope_piles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC02AEA9-EA56-1649-9CD0-1ADB754CC06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12967D2-A998-D342-B5ED-43CABE326A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18260" yWindow="3440" windowWidth="44060" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15680" yWindow="4780" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="319">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -343,9 +343,6 @@
     <t>vg</t>
   </si>
   <si>
-    <t>van Genuchten model (a, n)</t>
-  </si>
-  <si>
     <t>pow</t>
   </si>
   <si>
@@ -875,9 +872,6 @@
   </si>
   <si>
     <t>I</t>
-  </si>
-  <si>
-    <t>Fixity</t>
   </si>
   <si>
     <t>P</t>
@@ -1113,6 +1107,36 @@
       </rPr>
       <t>sat</t>
     </r>
+  </si>
+  <si>
+    <t>yr</t>
+  </si>
+  <si>
+    <t>Adhesion</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>1D element size:</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>Pinned</t>
+  </si>
+  <si>
+    <t>Unrotated</t>
+  </si>
+  <si>
+    <t>van Genuchten model (a, n, l)</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
 </sst>
 </file>
@@ -1574,16 +1598,16 @@
     <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1883,16 +1907,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>217714</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>54430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>199571</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9071</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>90714</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1907,8 +1931,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14804571" y="254001"/>
-          <a:ext cx="3610429" cy="3746499"/>
+          <a:off x="16455571" y="254001"/>
+          <a:ext cx="3855358" cy="4027713"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2032,6 +2056,31 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Adhesion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = soii-reinforcement interface adhesion (blank</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = use Lp)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Delta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = soil-reinforcement interface friction angle (blank = use Lp)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Tend1, Tend2 </a:t>
           </a:r>
           <a:r>
@@ -2078,6 +2127,10 @@
             <a:rPr lang="en-US" sz="1100" b="0"/>
             <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
           </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2090,16 +2143,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>308429</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>290286</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:rowOff>126999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>145143</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>553358</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2114,8 +2167,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13398500" y="190499"/>
-          <a:ext cx="3156858" cy="2349501"/>
+          <a:off x="14205857" y="126999"/>
+          <a:ext cx="3156858" cy="2521858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2420,7 +2473,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Fixity</a:t>
+            <a:t>Head</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
@@ -2432,8 +2485,54 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> = Pile head status (fixed or free)</a:t>
+            <a:t> = Pile head fixity status</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tip</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile tip fixity status</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -2760,7 +2859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
@@ -2785,15 +2884,15 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
       <c r="F7" s="15" t="s">
         <v>4</v>
       </c>
@@ -2961,7 +3060,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C20" s="14" t="s">
-        <v>45</v>
+        <v>312</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -2973,7 +3072,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C21" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>49</v>
@@ -2985,28 +3084,34 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>48</v>
+      </c>
       <c r="F22" s="1"/>
+      <c r="D22"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
-      <c r="C24" s="14" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D24"/>
+      <c r="D25"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
@@ -3048,93 +3153,98 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D59" s="1" t="s">
-        <v>62</v>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D58" s="1" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D60" s="1" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D61" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D62" s="1" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D63" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D66" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D68" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D69" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D70" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D71" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D72" s="1" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D73" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D74" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D75" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D76" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D77" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D78" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D79" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3143,28 +3253,28 @@
     <mergeCell ref="B7:D7"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$D$50:$D$51</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$D$54:$D$57</formula1>
+      <formula1>$D$54:$D$58</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>$D$60:$D$61</formula1>
+      <formula1>$D$61:$D$62</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>$D$64:$D$71</formula1>
+      <formula1>$D$65:$D$72</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000005000000}">
-      <formula1>$D$74:$D$78</formula1>
+      <formula1>$D$75:$D$79</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D25" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"circular,non-circular"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3174,83 +3284,89 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A2:AB25"/>
+  <dimension ref="A2:AD25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="6" width="10.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="10" max="12" width="10.83203125" style="1" customWidth="1"/>
-    <col min="16" max="18" width="10.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.33203125" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="20" width="10.83203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="R2" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="S2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="T2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="Q2" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="R2" s="28" t="s">
+      <c r="AB2" t="s">
         <v>257</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AC2" t="s">
         <v>258</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AD2" t="s">
         <v>259</v>
       </c>
-      <c r="AB2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3261,11 +3377,11 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
+        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J3" s="3"/>
@@ -3277,17 +3393,19 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-      <c r="Z3" t="s">
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="AB3" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC3" t="s">
         <v>261</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AD3" t="s">
         <v>262</v>
       </c>
-      <c r="AB3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3314,11 +3432,13 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-      <c r="Z4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="AB4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -3345,11 +3465,13 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="Z5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="AB5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -3376,8 +3498,10 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -3404,8 +3528,10 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -3432,17 +3558,19 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="Z8" t="s">
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="AB8" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC8" t="s">
         <v>258</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AD8" t="s">
         <v>259</v>
       </c>
-      <c r="AB8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -3469,17 +3597,19 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="Z9" t="s">
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="AB9" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC9" t="s">
         <v>261</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AD9" t="s">
         <v>262</v>
       </c>
-      <c r="AB9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -3506,17 +3636,19 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="Z10" t="s">
-        <v>264</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>262</v>
-      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
       <c r="AB10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3543,17 +3675,19 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="Z11" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>262</v>
-      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
       <c r="AB11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3580,8 +3714,10 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -3608,8 +3744,10 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -3636,8 +3774,10 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -3664,8 +3804,10 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -3692,8 +3834,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -3720,8 +3864,10 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -3748,8 +3894,10 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -3776,8 +3924,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -3804,8 +3954,10 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -3832,8 +3984,10 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -3860,39 +4014,41 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="T23" s="42"/>
-      <c r="U23" t="s">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V23" s="42"/>
+      <c r="W23" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="26"/>
+      <c r="W24" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="9" t="s">
-        <v>104</v>
+      <c r="V25" s="29"/>
+      <c r="W25" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G22" xr:uid="{00000000-0002-0000-0900-000000000000}">
-      <formula1>$Z$2:$Z$5</formula1>
+      <formula1>$AB$2:$AB$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H22" xr:uid="{00000000-0002-0000-0900-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+      <formula1>$AC$2:$AC$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I22" xr:uid="{00000000-0002-0000-0900-000002000000}">
-      <formula1>$AB$2:$AB$3</formula1>
+      <formula1>$AD$2:$AD$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3902,74 +4058,77 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:Z17"/>
+  <dimension ref="A2:AA17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
     <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="16" width="10.83203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.5" customWidth="1"/>
+    <col min="9" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>246</v>
-      </c>
       <c r="G2" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="I2" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="H2" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="I2" s="27" t="s">
+      <c r="J2" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="M2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="N2" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="M2" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>271</v>
-      </c>
       <c r="O2" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>222</v>
+        <v>313</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>314</v>
       </c>
       <c r="Z2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -4018,14 +4177,19 @@
           <t>free</t>
         </is>
       </c>
-      <c r="Y3" t="s">
-        <v>226</v>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
       </c>
       <c r="Z3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -4074,8 +4238,16 @@
           <t>free</t>
         </is>
       </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="Z4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -4094,8 +4266,12 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q5" s="3"/>
+      <c r="Z5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -4114,8 +4290,9 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -4134,8 +4311,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -4154,8 +4332,9 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -4174,8 +4353,9 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -4194,8 +4374,9 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -4214,8 +4395,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -4234,36 +4416,37 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R15" s="42"/>
-      <c r="S15" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S15" s="42"/>
+      <c r="T15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R16" s="26"/>
-      <c r="S16" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="18:19" x14ac:dyDescent="0.2">
-      <c r="R17" s="29"/>
-      <c r="S17" s="9" t="s">
-        <v>104</v>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S16" s="26"/>
+      <c r="T16" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="29"/>
+      <c r="T17" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
-      <formula1>$Y$2:$Y$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$Z$2:$Z$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4283,22 +4466,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="E2" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4521,99 +4704,99 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
+        <v>274</v>
+      </c>
+      <c r="F2" s="54"/>
+      <c r="H2" s="59" t="s">
+        <v>275</v>
+      </c>
+      <c r="I2" s="54"/>
+      <c r="K2" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="F2" s="52"/>
-      <c r="H2" s="59" t="s">
+      <c r="L2" s="54"/>
+      <c r="N2" s="59" t="s">
         <v>277</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="K2" s="59" t="s">
+      <c r="O2" s="54"/>
+      <c r="Q2" s="59" t="s">
         <v>278</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="N2" s="59" t="s">
-        <v>279</v>
-      </c>
-      <c r="O2" s="52"/>
-      <c r="Q2" s="59" t="s">
-        <v>280</v>
-      </c>
-      <c r="R2" s="52"/>
+      <c r="R2" s="54"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F3" s="33"/>
       <c r="H3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I3" s="33"/>
       <c r="K3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U4" t="s">
         <v>281</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4630,10 +4813,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="U5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4650,7 +4833,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4939,99 +5122,99 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
+        <v>286</v>
+      </c>
+      <c r="F2" s="54"/>
+      <c r="H2" s="60" t="s">
+        <v>287</v>
+      </c>
+      <c r="I2" s="54"/>
+      <c r="K2" s="60" t="s">
         <v>288</v>
       </c>
-      <c r="F2" s="52"/>
-      <c r="H2" s="60" t="s">
+      <c r="L2" s="54"/>
+      <c r="N2" s="60" t="s">
         <v>289</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="K2" s="60" t="s">
+      <c r="O2" s="54"/>
+      <c r="Q2" s="60" t="s">
         <v>290</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="N2" s="60" t="s">
-        <v>291</v>
-      </c>
-      <c r="O2" s="52"/>
-      <c r="Q2" s="60" t="s">
-        <v>292</v>
-      </c>
-      <c r="R2" s="52"/>
+      <c r="R2" s="54"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U4" t="s">
         <v>281</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5048,10 +5231,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="U5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5350,22 +5533,22 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>295</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>296</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>297</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5376,7 +5559,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -5398,7 +5581,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -5420,7 +5603,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -5432,7 +5615,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -5444,7 +5627,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -5464,7 +5647,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="J11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -6275,16 +6458,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:AP52"/>
+  <dimension ref="A2:AQ52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="41" width="8.5" customWidth="1"/>
+    <col min="11" max="42" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>79</v>
       </c>
@@ -6299,7 +6482,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>83</v>
       </c>
@@ -6320,7 +6503,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>89</v>
       </c>
@@ -6342,241 +6525,245 @@
         <v>93</v>
       </c>
       <c r="AK4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C5" s="1" t="s">
+      <c r="D5" t="s">
         <v>95</v>
-      </c>
-      <c r="D5" t="s">
-        <v>96</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AJ5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AK5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" t="s">
         <v>105</v>
-      </c>
-      <c r="P6" t="s">
-        <v>106</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C9" s="51" t="s">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C9" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="52"/>
-      <c r="Q9" s="52"/>
-      <c r="R9" s="52"/>
-      <c r="S9" s="52"/>
-      <c r="T9" s="52"/>
-      <c r="U9" s="52"/>
-      <c r="V9" s="52"/>
-      <c r="W9" s="52"/>
-      <c r="X9" s="52"/>
-      <c r="Y9" s="52"/>
-      <c r="Z9" s="52"/>
-      <c r="AA9" s="51" t="s">
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="54"/>
+      <c r="AD9" s="54"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="54"/>
+      <c r="AG9" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="AB9" s="52"/>
-      <c r="AC9" s="52"/>
-      <c r="AD9" s="52"/>
-      <c r="AE9" s="52"/>
-      <c r="AF9" s="52"/>
-      <c r="AG9" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="AH9" s="52"/>
-      <c r="AI9" s="52"/>
-      <c r="AJ9" s="52"/>
-      <c r="AK9" s="52"/>
-      <c r="AL9" s="52"/>
-      <c r="AM9" s="52"/>
-      <c r="AN9" s="52"/>
-      <c r="AO9" s="52"/>
-      <c r="AP9" s="52"/>
-    </row>
-    <row r="10" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AH9" s="54"/>
+      <c r="AI9" s="54"/>
+      <c r="AJ9" s="54"/>
+      <c r="AK9" s="54"/>
+      <c r="AL9" s="54"/>
+      <c r="AM9" s="54"/>
+      <c r="AN9" s="54"/>
+      <c r="AO9" s="54"/>
+      <c r="AP9" s="54"/>
+      <c r="AQ9" s="54"/>
+    </row>
+    <row r="10" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="D10" s="48" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="44" t="s">
+      <c r="F10" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="G10" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="I10" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="J10" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="K10" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="K10" s="49" t="s">
+      <c r="L10" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="M10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="N10" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="N10" s="43" t="s">
+      <c r="O10" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="O10" s="44" t="s">
+      <c r="P10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="P10" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10" s="44" t="s">
+      <c r="R10" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="T10" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="T10" s="44" t="s">
+      <c r="U10" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="V10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="V10" s="44" t="s">
+      <c r="W10" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="W10" s="44" t="s">
+      <c r="X10" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="X10" s="44" t="s">
+      <c r="Y10" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="Y10" s="44" t="s">
+      <c r="Z10" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="Z10" s="44" t="s">
+      <c r="AA10" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB10" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC10" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="AA10" s="46" t="s">
+      <c r="AD10" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE10" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="AB10" s="46" t="s">
-        <v>305</v>
-      </c>
-      <c r="AC10" s="47" t="s">
+      <c r="AF10" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="AD10" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="AE10" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>309</v>
-      </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AI10" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AM10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AN10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="AP10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AO10" s="23" t="s">
+      <c r="AQ10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AP10" s="23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -6613,7 +6800,7 @@
         <v>0.0</v>
       </c>
       <c r="L11" s="3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M11" s="3">
         <v>2000000.0</v>
@@ -6699,10 +6886,13 @@
       <c r="AN11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AO11" s="3"/>
+      <c r="AO11" s="3">
+        <v>0.5</v>
+      </c>
       <c r="AP11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ11" s="3"/>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -6747,8 +6937,9 @@
       <c r="AN12" s="19"/>
       <c r="AO12" s="19"/>
       <c r="AP12" s="19"/>
-    </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ12" s="19"/>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -6793,8 +6984,9 @@
       <c r="AN13" s="19"/>
       <c r="AO13" s="19"/>
       <c r="AP13" s="19"/>
-    </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ13" s="19"/>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -6839,8 +7031,9 @@
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ14" s="3"/>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -6885,8 +7078,9 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ15" s="3"/>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>6</v>
       </c>
@@ -6931,8 +7125,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
-    </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ16" s="3"/>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>7</v>
       </c>
@@ -6977,8 +7172,9 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
-    </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ17" s="3"/>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>8</v>
       </c>
@@ -7023,8 +7219,9 @@
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
-    </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ18" s="3"/>
+    </row>
+    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>9</v>
       </c>
@@ -7069,8 +7266,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
-    </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ19" s="3"/>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>10</v>
       </c>
@@ -7115,8 +7313,9 @@
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
-    </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ20" s="3"/>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>11</v>
       </c>
@@ -7161,8 +7360,9 @@
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
-    </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ21" s="3"/>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>12</v>
       </c>
@@ -7207,8 +7407,9 @@
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
-    </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ22" s="3"/>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -7253,8 +7454,9 @@
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
-    </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ23" s="3"/>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -7299,8 +7501,9 @@
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
-    </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ24" s="3"/>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -7345,8 +7548,9 @@
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
-    </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ25" s="3"/>
+    </row>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -7379,8 +7583,9 @@
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
-    </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ26" s="1"/>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -7404,7 +7609,7 @@
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -7428,7 +7633,7 @@
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -7452,7 +7657,7 @@
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -7476,7 +7681,7 @@
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -7500,7 +7705,7 @@
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -8006,7 +8211,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="AG9:AP9"/>
+    <mergeCell ref="AG9:AQ9"/>
     <mergeCell ref="AA9:AF9"/>
     <mergeCell ref="C9:Z9"/>
   </mergeCells>
@@ -8086,7 +8291,7 @@
       <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM11:AN52">
+  <conditionalFormatting sqref="AM11:AO52">
     <cfRule type="expression" dxfId="18" priority="1">
       <formula>$AJ11="lf"</formula>
     </cfRule>
@@ -8134,16 +8339,16 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B2" s="3">
         <v>-10.0</v>
       </c>
       <c r="D2" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="N2" s="24" t="s">
         <v>147</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -8152,167 +8357,167 @@
           <t>Profile Line #1</t>
         </is>
       </c>
-      <c r="B4" s="53"/>
+      <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="52"/>
+      <c r="G4" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="G4" s="55" t="s">
+      <c r="H4" s="52"/>
+      <c r="J4" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="J4" s="55" t="s">
+      <c r="K4" s="52"/>
+      <c r="M4" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="M4" s="55" t="s">
+      <c r="N4" s="52"/>
+      <c r="P4" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="N4" s="53"/>
-      <c r="P4" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q4" s="52"/>
+      <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="T4" s="52"/>
+        <v>154</v>
+      </c>
+      <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>156</v>
-      </c>
-      <c r="W4" s="52"/>
+        <v>155</v>
+      </c>
+      <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z4" s="52"/>
+        <v>156</v>
+      </c>
+      <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC4" s="54"/>
+      <c r="AE4" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="AC4" s="52"/>
-      <c r="AE4" s="55" t="s">
-        <v>159</v>
-      </c>
-      <c r="AF4" s="52"/>
+      <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="AI4" s="52"/>
+        <v>159</v>
+      </c>
+      <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL4" s="52"/>
+        <v>160</v>
+      </c>
+      <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>162</v>
-      </c>
-      <c r="AO4" s="52"/>
+        <v>161</v>
+      </c>
+      <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>163</v>
-      </c>
-      <c r="AR4" s="52"/>
+        <v>162</v>
+      </c>
+      <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -8321,7 +8526,7 @@
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>soil</v>
       </c>
       <c r="B6" s="57"/>
       <c r="D6" s="56" t="str">
@@ -8405,172 +8610,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -9454,277 +9659,277 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="52"/>
+      <c r="D4" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="D4" s="55" t="s">
+      <c r="E4" s="52"/>
+      <c r="G4" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="G4" s="55" t="s">
+      <c r="H4" s="52"/>
+      <c r="J4" s="55" t="s">
         <v>172</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="J4" s="55" t="s">
+      <c r="K4" s="52"/>
+      <c r="M4" s="55" t="s">
         <v>173</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="M4" s="55" t="s">
+      <c r="N4" s="52"/>
+      <c r="P4" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="N4" s="53"/>
-      <c r="P4" s="55" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q4" s="52"/>
+      <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>176</v>
-      </c>
-      <c r="T4" s="52"/>
+        <v>175</v>
+      </c>
+      <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>177</v>
-      </c>
-      <c r="W4" s="52"/>
+        <v>176</v>
+      </c>
+      <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z4" s="52"/>
+        <v>177</v>
+      </c>
+      <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
+        <v>178</v>
+      </c>
+      <c r="AC4" s="54"/>
+      <c r="AE4" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="AC4" s="52"/>
-      <c r="AE4" s="55" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF4" s="52"/>
+      <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="AI4" s="52"/>
+        <v>180</v>
+      </c>
+      <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="AL4" s="52"/>
+        <v>181</v>
+      </c>
+      <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="AO4" s="52"/>
+        <v>182</v>
+      </c>
+      <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>184</v>
-      </c>
-      <c r="AR4" s="52"/>
+        <v>183</v>
+      </c>
+      <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="D5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="G5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="H5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="J5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="K5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="K5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="M5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="N5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="N5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="P5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Q5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="T5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="T5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="W5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="W5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Z5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="AC5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="AE5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AF5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AF5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AI5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AL5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AO5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AO5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AR5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AR5" s="39" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K6" s="39">
         <v>4</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N6" s="39">
         <v>5</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q6" s="39">
         <v>6</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T6" s="39">
         <v>7</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W6" s="39">
         <v>8</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -9733,7 +9938,7 @@
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="58" t="str">
         <f>IF(OR(B5="",B5="material"),_xlfn.XLOOKUP(B6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>soil</v>
       </c>
       <c r="B7" s="57"/>
       <c r="D7" s="58" t="str">
@@ -9817,172 +10022,172 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B8" s="39"/>
       <c r="D8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N8" s="39"/>
       <c r="P8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W8" s="39"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -10787,10 +10992,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="M7:N7"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="P4:Q4"/>
@@ -10799,12 +11000,13 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="V7:W7"/>
     <mergeCell ref="P7:Q7"/>
     <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="S4:T4"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH4:AI4"/>
@@ -10817,6 +11019,9 @@
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="AN7:AO7"/>
     <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="V7:W7"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -10913,20 +11118,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="D2" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="D2" s="60" t="s">
+      <c r="E2" s="54"/>
+      <c r="G2" s="22" t="s">
         <v>188</v>
-      </c>
-      <c r="E2" s="52"/>
-      <c r="G2" s="22" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -10934,7 +11139,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -10945,19 +11150,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -10970,7 +11175,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -10979,10 +11184,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" t="s">
         <v>192</v>
-      </c>
-      <c r="H6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -11119,31 +11324,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -11171,10 +11376,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -11189,10 +11394,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -11207,10 +11412,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K5" t="s">
         <v>206</v>
-      </c>
-      <c r="K5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -11237,7 +11442,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -11252,7 +11457,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K8"/>
     </row>
@@ -11268,7 +11473,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9"/>
     </row>
@@ -11284,7 +11489,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K10"/>
     </row>
@@ -11300,7 +11505,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K11"/>
     </row>
@@ -11316,31 +11521,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -11349,7 +11554,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K17"/>
     </row>
@@ -11390,16 +11595,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -11410,10 +11615,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" t="s">
         <v>222</v>
-      </c>
-      <c r="F3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -11421,10 +11626,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" t="s">
         <v>224</v>
-      </c>
-      <c r="F4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -11432,10 +11637,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5" t="s">
         <v>226</v>
-      </c>
-      <c r="F5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11559,128 +11764,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12108,128 +12313,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
